--- a/NRHS/Output/NRHS_Timetable_Final.xlsx
+++ b/NRHS/Output/NRHS_Timetable_Final.xlsx
@@ -653,12 +653,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr"/>
       <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
@@ -676,12 +676,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr"/>
       <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
@@ -698,18 +698,18 @@
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="7" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
+      <c r="F7" s="7" t="inlineStr"/>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
@@ -721,12 +721,12 @@
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
@@ -744,18 +744,18 @@
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
@@ -773,12 +773,12 @@
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr"/>
@@ -853,32 +853,32 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
@@ -900,34 +900,30 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
+      <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (HIN)</t>
@@ -952,32 +948,32 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (HIN)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (HIN)</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -1004,23 +1000,23 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (EVS)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (HIN)</t>
+          <t>UKG (A) (TEL)</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -1037,17 +1033,17 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ORAL)</t>
+          <t>UKG (A) (EVS)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -1080,33 +1076,37 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
-        </is>
-      </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (HIN)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
@@ -1183,10 +1183,14 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
@@ -1208,11 +1212,7 @@
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr"/>
@@ -1251,12 +1251,12 @@
       <c r="B26" s="7" t="inlineStr"/>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr"/>
@@ -1271,17 +1271,17 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
@@ -1294,15 +1294,15 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr"/>
@@ -1384,28 +1384,28 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr"/>
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -1423,26 +1423,30 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr"/>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (MATH)</t>
+          <t>Class 7 (G.K)</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -1469,23 +1473,19 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -1502,28 +1502,28 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (G.K)</t>
+          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 6 (MATH)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -1546,28 +1546,28 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -1584,33 +1584,33 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (G.K)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (ENG)</t>
+          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (ENG)</t>
+          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -1732,22 +1732,22 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (ENG)</t>
+          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (ENG)</t>
+          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -1788,20 +1788,20 @@
           <t>Class 1(A) (MATH)</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (G.K)</t>
+          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (TEL)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -1818,32 +1818,32 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (G.K)</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
@@ -1861,33 +1861,33 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (G.K)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (TEL)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -1904,33 +1904,33 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (TEL)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (ENG)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -2017,11 +2017,7 @@
           <t>Class 9 (MATH)</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="H50" s="7" t="inlineStr"/>
       <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
@@ -2044,11 +2040,7 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="8" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -2066,10 +2058,14 @@
       <c r="D52" s="7" t="inlineStr"/>
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (MATH)</t>
+          <t>Class 9 (MATH)</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
@@ -2089,8 +2085,16 @@
       <c r="D53" s="7" t="inlineStr"/>
       <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr"/>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
@@ -2108,19 +2112,15 @@
       <c r="D54" s="7" t="inlineStr"/>
       <c r="E54" s="7" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
     </row>
@@ -2135,15 +2135,15 @@
       <c r="D55" s="7" t="inlineStr"/>
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
     </row>
@@ -2220,12 +2220,12 @@
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr"/>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
+      <c r="D59" s="7" t="inlineStr"/>
       <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
@@ -2246,29 +2246,29 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr"/>
+      <c r="C60" s="7" t="inlineStr"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr"/>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2277,28 +2277,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr"/>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
     </row>
@@ -2308,10 +2308,14 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr"/>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (ENG)</t>
+          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -2319,17 +2323,13 @@
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
+      <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr"/>
     </row>
@@ -2339,26 +2339,26 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr"/>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr"/>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr"/>
@@ -2370,13 +2370,17 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr"/>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr"/>
+      <c r="C64" s="7" t="inlineStr"/>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
@@ -2387,11 +2391,7 @@
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="G64" s="7" t="inlineStr"/>
       <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr"/>
     </row>
@@ -2463,25 +2463,33 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr"/>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Class 9 (CHEM)</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr"/>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="7" t="inlineStr"/>
       <c r="I68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2496,15 +2504,27 @@
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
       <c r="I69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2515,7 +2535,7 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr"/>
@@ -2535,11 +2555,7 @@
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
+      <c r="H70" s="7" t="inlineStr"/>
       <c r="I70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2550,25 +2566,21 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 8 (G.K)</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr"/>
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
@@ -2581,31 +2593,35 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (CHEM)</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="H72" s="7" t="inlineStr">
         <is>
           <t>Class 6 (PHY)</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2616,27 +2632,35 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (CHEM)</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr">
         <is>
           <t>Class 8 (PHY)</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
       <c r="I73" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2717,23 +2741,23 @@
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr"/>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
+      <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
@@ -2742,28 +2766,28 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr"/>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr"/>
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
+      <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -2785,7 +2809,7 @@
       <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -2801,7 +2825,7 @@
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr"/>
@@ -2814,31 +2838,31 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr"/>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="G80" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr"/>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
@@ -2849,29 +2873,29 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr"/>
@@ -2884,15 +2908,15 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr"/>
+      <c r="C82" s="7" t="inlineStr"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
@@ -2906,7 +2930,7 @@
       <c r="G82" s="7" t="inlineStr"/>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr"/>
@@ -2981,22 +3005,22 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (EVS)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (TEL)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -3004,14 +3028,10 @@
           <t>UKG (B) (ENG)</t>
         </is>
       </c>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -3028,37 +3048,33 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (MATH)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -3075,37 +3091,37 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (MATH)</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (HIN)</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -3122,30 +3138,34 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (MATH)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (HIN)</t>
@@ -3170,22 +3190,22 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ENG)</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (TEL)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
@@ -3208,30 +3228,34 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ENG)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (MATH)</t>
+          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr"/>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (HIN)</t>
@@ -3318,28 +3342,28 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (G.K)</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
@@ -3356,17 +3380,17 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr"/>
@@ -3377,12 +3401,12 @@
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3402,30 +3426,26 @@
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I97" s="8" t="inlineStr">
@@ -3452,7 +3472,7 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr"/>
@@ -3484,30 +3504,26 @@
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr"/>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -3527,27 +3543,23 @@
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
+      <c r="G100" s="7" t="inlineStr"/>
       <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
@@ -3632,7 +3644,11 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr"/>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
           <t>Class 2 (G.K)</t>
@@ -3640,15 +3656,15 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr"/>
       <c r="H104" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
@@ -3673,26 +3689,26 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr"/>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
+      <c r="E105" s="7" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
+      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3707,35 +3723,31 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
+          <t>Class 2 (TEL)</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
+      <c r="D106" s="7" t="inlineStr"/>
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>LKG (TEL)</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
+      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3755,18 +3767,18 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
           <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr"/>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -3789,31 +3801,31 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3831,28 +3843,28 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr"/>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr"/>
-      <c r="H109" s="7" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
+      <c r="H109" s="7" t="inlineStr"/>
       <c r="I109" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3934,25 +3946,21 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr"/>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="7" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
+      <c r="G113" s="7" t="inlineStr"/>
       <c r="H113" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
@@ -3977,18 +3985,18 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr"/>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="E114" s="7" t="inlineStr"/>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr"/>
@@ -4011,31 +4019,35 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (G.K)</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr"/>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (SOC)</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4058,12 +4070,12 @@
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr"/>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="D116" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
+      <c r="E116" s="7" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
@@ -4094,7 +4106,7 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr"/>
@@ -4105,7 +4117,7 @@
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 3 (SOC)</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr"/>
@@ -4133,26 +4145,26 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr"/>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr"/>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="G118" s="7" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4231,13 +4243,13 @@
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="7" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr"/>
-      <c r="F122" s="7" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="G122" s="7" t="inlineStr"/>
-      <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
@@ -4256,16 +4268,16 @@
       <c r="E123" s="7" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
           <t>Class 8 (HIN)</t>
         </is>
       </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="H123" s="7" t="inlineStr"/>
-      <c r="I123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -4283,7 +4295,11 @@
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr"/>
-      <c r="H124" s="7" t="inlineStr"/>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (HIN)</t>
+        </is>
+      </c>
       <c r="I124" s="8" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
@@ -4302,14 +4318,10 @@
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
+      <c r="G125" s="7" t="inlineStr"/>
       <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
@@ -4329,18 +4341,18 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (HIN)</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr"/>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr"/>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="I126" s="8" t="inlineStr">
-        <is>
-          <t>Class 8 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4371,12 @@
           <t>Class 10 (HIN)</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr"/>
-      <c r="H127" s="7" t="inlineStr">
+      <c r="G127" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
+      <c r="H127" s="7" t="inlineStr"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
@@ -4439,39 +4451,31 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
+      <c r="B131" s="7" t="inlineStr"/>
       <c r="C131" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
+      <c r="F131" s="7" t="inlineStr"/>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I131" s="8" t="inlineStr">
@@ -4488,37 +4492,33 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
       <c r="E132" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr"/>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="F132" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="inlineStr">
+      <c r="H132" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
@@ -4533,11 +4533,7 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
-        </is>
-      </c>
+      <c r="B133" s="7" t="inlineStr"/>
       <c r="C133" s="7" t="inlineStr">
         <is>
           <t>Class 6 (BIO)</t>
@@ -4545,27 +4541,23 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr"/>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="H133" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H133" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="I133" s="8" t="inlineStr">
@@ -4582,32 +4574,28 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 5 (G.K)</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
+      <c r="D134" s="7" t="inlineStr"/>
       <c r="E134" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr"/>
@@ -4625,33 +4613,33 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
       <c r="G135" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -4668,28 +4656,28 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (BIO)</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (MATH)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
@@ -4773,7 +4761,7 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (G.K)</t>
+          <t>Class 4 (HIN)</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -4781,18 +4769,22 @@
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr"/>
-      <c r="E140" s="7" t="inlineStr">
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr"/>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr"/>
       <c r="H140" s="7" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
@@ -4808,15 +4800,15 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr"/>
-      <c r="D141" s="7" t="inlineStr">
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
+      <c r="D141" s="7" t="inlineStr"/>
       <c r="E141" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
@@ -4827,7 +4819,11 @@
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="G141" s="7" t="inlineStr"/>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
       <c r="H141" s="7" t="inlineStr"/>
       <c r="I141" s="8" t="inlineStr">
         <is>
@@ -4854,19 +4850,15 @@
       <c r="D142" s="7" t="inlineStr"/>
       <c r="E142" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+      <c r="G142" s="7" t="inlineStr"/>
       <c r="H142" s="7" t="inlineStr"/>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -4885,23 +4877,23 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr"/>
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr"/>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr"/>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
+      <c r="F143" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr"/>
       <c r="H143" s="7" t="inlineStr"/>
       <c r="I143" s="8" t="inlineStr">
         <is>
@@ -4922,18 +4914,18 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="E144" s="7" t="inlineStr"/>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr"/>
@@ -4957,25 +4949,21 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr"/>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr"/>
       <c r="H145" s="7" t="inlineStr"/>
       <c r="I145" s="8" t="inlineStr">
         <is>
@@ -5051,12 +5039,12 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr"/>
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
         </is>
       </c>
-      <c r="C149" s="7" t="inlineStr"/>
       <c r="D149" s="7" t="inlineStr"/>
       <c r="E149" s="7" t="inlineStr"/>
       <c r="F149" s="7" t="inlineStr"/>
@@ -5094,7 +5082,11 @@
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr"/>
-      <c r="C151" s="7" t="inlineStr"/>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="D151" s="7" t="inlineStr"/>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr"/>
@@ -5108,14 +5100,14 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="B152" s="7" t="inlineStr"/>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr"/>
-      <c r="E152" s="7" t="inlineStr"/>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="F152" s="7" t="inlineStr"/>
       <c r="G152" s="7" t="inlineStr"/>
       <c r="H152" s="7" t="inlineStr"/>
@@ -5153,11 +5145,7 @@
           <t>Class 10 (PHY)</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+      <c r="E154" s="7" t="inlineStr"/>
       <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="inlineStr"/>
       <c r="H154" s="7" t="inlineStr"/>
@@ -5233,37 +5221,37 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="C158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
@@ -5280,37 +5268,37 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="C159" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="D159" s="7" t="inlineStr">
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
         <is>
           <t>LKG (MATH)</t>
         </is>
       </c>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr">
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
         <is>
           <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
@@ -5332,28 +5320,32 @@
       </c>
       <c r="C160" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
           <t>LKG (ORAL)</t>
         </is>
       </c>
-      <c r="D160" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="E160" s="7" t="inlineStr"/>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
       <c r="G160" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="I160" s="8" t="inlineStr">
@@ -5370,37 +5362,33 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr"/>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="I161" s="8" t="inlineStr">
@@ -5417,28 +5405,28 @@
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr"/>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
           <t>LKG (MATH)</t>
         </is>
       </c>
-      <c r="C162" s="7" t="inlineStr">
+      <c r="G162" s="7" t="inlineStr">
         <is>
           <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="D162" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr"/>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -5460,28 +5448,28 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr"/>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
           <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="D163" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr"/>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
@@ -5569,15 +5557,15 @@
       <c r="E167" s="7" t="inlineStr"/>
       <c r="F167" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr"/>
-      <c r="H167" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
-        </is>
-      </c>
+      <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
@@ -5596,15 +5584,15 @@
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr"/>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="H168" s="7" t="inlineStr"/>
       <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
@@ -5650,15 +5638,15 @@
       <c r="E170" s="7" t="inlineStr"/>
       <c r="F170" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="G170" s="7" t="inlineStr"/>
-      <c r="H170" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
-        </is>
-      </c>
+      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
@@ -5677,18 +5665,18 @@
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5709,13 +5697,13 @@
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="H172" s="7" t="inlineStr"/>
       <c r="I172" s="8" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5789,31 +5777,31 @@
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr"/>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="D176" s="7" t="inlineStr"/>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr"/>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
+      <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
           <t>Class 1(B)</t>
@@ -5833,26 +5821,26 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr"/>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr"/>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (G.K)</t>
         </is>
       </c>
-      <c r="D177" s="7" t="inlineStr"/>
-      <c r="E177" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Class 1(B)</t>
@@ -5867,31 +5855,31 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="C178" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr"/>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr"/>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (G.K)</t>
+          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr"/>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Class 1(B)</t>
@@ -5906,26 +5894,30 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr"/>
-      <c r="D179" s="7" t="inlineStr">
+      <c r="D179" s="7" t="inlineStr"/>
+      <c r="E179" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="E179" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (HIN)</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr"/>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
       <c r="H179" s="7" t="inlineStr"/>
       <c r="I179" s="8" t="inlineStr">
         <is>
@@ -5941,31 +5933,31 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="C180" s="7" t="inlineStr"/>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (HIN)</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr"/>
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr"/>
-      <c r="H180" s="7" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
+      <c r="H180" s="7" t="inlineStr"/>
       <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Class 1(B)</t>
@@ -5980,18 +5972,14 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="C181" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
+          <t>Class 1(B) (G.K)</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr"/>
       <c r="D181" s="7" t="inlineStr"/>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (HIN)</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
@@ -6083,19 +6071,23 @@
       <c r="C185" s="7" t="inlineStr"/>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="F185" s="7" t="inlineStr"/>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
       <c r="G185" s="7" t="inlineStr"/>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 1(B) (COMP)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -6106,33 +6098,25 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B186" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
+      <c r="B186" s="7" t="inlineStr"/>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
+          <t>Class 6 (COMP)</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="inlineStr"/>
-      <c r="F186" s="7" t="inlineStr">
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
         <is>
           <t>Class 7 (COMP)</t>
         </is>
       </c>
+      <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr"/>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="H186" s="7" t="inlineStr"/>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
@@ -6146,24 +6130,28 @@
           <t>Class 8 (COMP)</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr"/>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="inlineStr">
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr"/>
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr"/>
-      <c r="G187" s="7" t="inlineStr"/>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (COMP)</t>
-        </is>
-      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (COMP)</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
@@ -6173,19 +6161,23 @@
         </is>
       </c>
       <c r="B188" s="7" t="inlineStr"/>
-      <c r="C188" s="7" t="inlineStr"/>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="E188" s="7" t="inlineStr"/>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
       <c r="F188" s="7" t="inlineStr"/>
-      <c r="G188" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="G188" s="7" t="inlineStr"/>
       <c r="H188" s="7" t="inlineStr"/>
       <c r="I188" s="7" t="inlineStr"/>
     </row>
@@ -6196,20 +6188,20 @@
         </is>
       </c>
       <c r="B189" s="7" t="inlineStr"/>
-      <c r="C189" s="7" t="inlineStr"/>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (COMP)</t>
+        </is>
+      </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
+      <c r="E189" s="7" t="inlineStr"/>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (COMP)</t>
+          <t>Class 8 (COMP)</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr"/>
@@ -6223,28 +6215,24 @@
         </is>
       </c>
       <c r="B190" s="7" t="inlineStr"/>
-      <c r="C190" s="7" t="inlineStr"/>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (COMP)</t>
+        </is>
+      </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
+          <t>Class 1(A) (COMP)</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr"/>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (COMP)</t>
+          <t>Class 3 (COMP)</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr"/>
-      <c r="H190" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
     <row r="192">
@@ -6322,12 +6310,12 @@
       <c r="F194" s="7" t="inlineStr"/>
       <c r="G194" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (P.E.T)</t>
         </is>
       </c>
       <c r="I194" s="7" t="inlineStr"/>
@@ -6345,12 +6333,12 @@
       <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (P.E.T)</t>
         </is>
       </c>
       <c r="I195" s="7" t="inlineStr"/>
@@ -6368,12 +6356,12 @@
       <c r="F196" s="7" t="inlineStr"/>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>LKG (P.E.T)</t>
+          <t>Class 6 (P.E.T)</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 7 (P.E.T)</t>
         </is>
       </c>
       <c r="I196" s="7" t="inlineStr"/>
@@ -6391,7 +6379,7 @@
       <c r="F197" s="7" t="inlineStr"/>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (P.E.T)</t>
+          <t>UKG (A) (P.E.T)</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr"/>
@@ -6410,12 +6398,12 @@
       <c r="F198" s="7" t="inlineStr"/>
       <c r="G198" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="inlineStr">
-        <is>
-          <t>LKG (P.E.T)</t>
         </is>
       </c>
       <c r="I198" s="7" t="inlineStr"/>
@@ -6433,12 +6421,12 @@
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>Class 3 (P.E.T)</t>
         </is>
       </c>
       <c r="I199" s="7" t="inlineStr"/>
@@ -6751,19 +6739,19 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (EVS)</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -6775,7 +6763,7 @@
       <c r="G2" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -6793,12 +6781,12 @@
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
-(G.K)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (EVS)</t>
         </is>
       </c>
@@ -6822,8 +6810,8 @@
       </c>
       <c r="O2" s="7" t="inlineStr">
         <is>
-          <t>SAIRAM
-(PHY)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -6840,26 +6828,26 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -6870,28 +6858,28 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
@@ -6904,21 +6892,22 @@
 (TEL)</t>
         </is>
       </c>
-      <c r="N3" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -6930,31 +6919,31 @@
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -6965,50 +6954,48 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O4" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -7020,19 +7007,19 @@
       <c r="C5" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (EVS)</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -7043,50 +7030,50 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(G.K)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
@@ -7109,13 +7096,13 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -7133,60 +7120,61 @@
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P6" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7198,33 +7186,33 @@
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
@@ -7233,49 +7221,50 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>S.GAYATHRI
+(MATH)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7276,7 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -7299,7 +7288,7 @@
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -7310,8 +7299,8 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(HIN)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -7322,14 +7311,14 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>N.NAVYA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -7340,8 +7329,8 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -7352,20 +7341,20 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>D.GOWTHAM
-(MATH)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -7473,25 +7462,25 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -7508,22 +7497,22 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -7536,16 +7525,15 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -7563,73 +7551,73 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
@@ -7653,7 +7641,7 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -7665,7 +7653,7 @@
       <c r="E12" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -7676,56 +7664,56 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>ANURADHA
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -7742,14 +7730,14 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>SHEKINA
+(ENG)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -7761,19 +7749,19 @@
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(ENG)</t>
+          <t>ANURADHA
+(EVS)</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(HIN)</t>
+          <t>S.GAYATHRI
+(EVS)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -7784,14 +7772,14 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
 (EVS)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -7802,19 +7790,19 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -7831,19 +7819,19 @@
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ORAL)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -7855,19 +7843,19 @@
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>P.SATYAVENI
+(G.K)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -7878,8 +7866,8 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -7890,20 +7878,20 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
@@ -7921,31 +7909,31 @@
       <c r="C15" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(ENG)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -7956,44 +7944,44 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -8011,7 +7999,7 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -8023,49 +8011,49 @@
       <c r="E16" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (HIN)</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>N.NAVYA
-(ENG)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>K.ESWAR
+(PHY)</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -8076,14 +8064,14 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
         <is>
-          <t>D.GOWTHAM
-(MATH)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
@@ -8166,9 +8154,10 @@
 (CLASS)</t>
         </is>
       </c>
-      <c r="N17" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N17" s="8" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="O17" s="8" t="inlineStr">
@@ -8208,25 +8197,25 @@
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(G.K)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -8243,14 +8232,14 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
 (G.K)</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -8273,8 +8262,8 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8286,13 +8275,13 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (ORAL)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -8309,28 +8298,28 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(MATH)</t>
+          <t>ANURADHA
+(EVS)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -8349,15 +8338,16 @@
 (HIN)</t>
         </is>
       </c>
-      <c r="N19" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
       <c r="P19" s="7" t="inlineStr">
@@ -8375,19 +8365,19 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (EVS)</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -8398,8 +8388,8 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>ANURADHA
-(EVS)</t>
+          <t>SURYA DEVI
+(ENG)</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -8411,27 +8401,27 @@
       <c r="I20" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
@@ -8440,8 +8430,8 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
@@ -8450,10 +8440,9 @@
 (BIO)</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8460,7 @@
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -8482,46 +8471,46 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>ANURADHA
+(EVS)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(G.K)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(MATH)</t>
+          <t>SHEKINA
+(HIN)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
@@ -8534,9 +8523,10 @@
 (PHY)</t>
         </is>
       </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr">
@@ -8553,55 +8543,55 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -8642,52 +8632,52 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
       <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
@@ -8696,8 +8686,8 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -8720,8 +8710,8 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>D.GOWTHAM
+(MATH)</t>
         </is>
       </c>
     </row>
@@ -8733,85 +8723,85 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (MATH)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (HIN)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
       <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8909,7 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -8931,19 +8921,19 @@
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (TEL)</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -8967,7 +8957,7 @@
       <c r="K26" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -8979,25 +8969,25 @@
       <c r="M26" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
 (G.K)</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -9008,85 +8998,86 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="M27" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="N27" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -9098,61 +9089,61 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
 (EVS)</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -9161,21 +9152,20 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="N28" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="P28" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9187,19 +9177,19 @@
       <c r="C29" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -9211,7 +9201,7 @@
       <c r="G29" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -9222,49 +9212,50 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
       <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O29" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -9275,20 +9266,20 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (ENG)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -9323,38 +9314,38 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
-        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(PHY)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9365,46 +9356,46 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(G.K)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>SURYA DEVI
+(MATH)</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
@@ -9425,26 +9416,26 @@
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>D.GOWTHAM
+(MATH)</t>
         </is>
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9456,13 +9447,13 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -9527,14 +9518,13 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P32" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9642,13 +9632,13 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -9660,39 +9650,39 @@
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
       <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -9707,20 +9697,20 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="O34" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9722,7 @@
       <c r="C35" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -9744,72 +9734,73 @@
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
           <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O35" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="O35" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P35" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9827,19 +9818,19 @@
       <c r="D36" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ANURADHA
-(EVS)</t>
+          <t>CHANDRAKALA
+(G.K)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -9850,50 +9841,49 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
       <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O36" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
@@ -9910,8 +9900,8 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -9929,25 +9919,25 @@
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
@@ -9958,36 +9948,36 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P37" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -9998,86 +9988,86 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="O38" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -10089,7 +10079,7 @@
       <c r="C39" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -10106,68 +10096,68 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr">
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="P39" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -10197,13 +10187,13 @@
       <c r="F40" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(ENG)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -10214,50 +10204,50 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O40" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -10336,22 +10326,22 @@
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
           <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
+      <c r="P41" s="8" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
@@ -10365,31 +10355,31 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -10412,8 +10402,8 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -10424,26 +10414,26 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(G.K)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -10455,7 +10445,7 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -10467,33 +10457,33 @@
       <c r="E43" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(ENG)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -10502,37 +10492,36 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N43" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="O43" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P43" s="12" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N43" s="12" t="inlineStr">
         <is>
           <t>Recreation</t>
+        </is>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -10550,19 +10539,19 @@
       <c r="D44" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(ENG)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -10573,26 +10562,26 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>K.ESWAR
+(EVS)</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -10603,19 +10592,20 @@
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(BIO)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="O44" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -10632,58 +10622,58 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
@@ -10692,20 +10682,18 @@
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="O45" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="P45" s="7" t="inlineStr">
@@ -10722,62 +10710,62 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -10813,85 +10801,85 @@
       <c r="C47" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (MATH)</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+(BIO)</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N47" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
       <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10897,7 @@
       <c r="D48" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -10921,13 +10909,13 @@
       <c r="F48" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -10938,8 +10926,8 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
@@ -10950,38 +10938,38 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O48" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="P48" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -11066,14 +11054,14 @@
       </c>
       <c r="O49" s="8" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
           <t>D.GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="P49" s="8" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>

--- a/NRHS/Output/NRHS_Timetable_Final.xlsx
+++ b/NRHS/Output/NRHS_Timetable_Final.xlsx
@@ -656,16 +656,16 @@
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
@@ -675,18 +675,18 @@
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr"/>
-      <c r="C6" s="7" t="inlineStr"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
+      <c r="F6" s="7" t="inlineStr"/>
       <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="7" t="inlineStr"/>
@@ -721,15 +721,15 @@
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr"/>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
@@ -744,18 +744,18 @@
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr"/>
-      <c r="C9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
       <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
+      <c r="F9" s="7" t="inlineStr"/>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
@@ -773,12 +773,12 @@
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
+      <c r="F10" s="7" t="inlineStr"/>
       <c r="G10" s="7" t="inlineStr"/>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="7" t="inlineStr"/>
@@ -853,37 +853,33 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (EVS)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
+          <t>UKG (A) (HIN)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (HIN)</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
@@ -900,33 +896,37 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (MATH)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (MATH)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (HIN)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (HIN)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -943,37 +943,37 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (EVS)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (EVS)</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (HIN)</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ORAL)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (MATH)</t>
+          <t>UKG (A) (HIN)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (MATH)</t>
+          <t>UKG (A) (TEL)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1010,13 +1010,13 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (EVS)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (TEL)</t>
+          <t>UKG (A) (ORAL)</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
@@ -1033,33 +1033,33 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (HIN)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -1081,14 +1081,14 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (HIN)</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1193,7 +1193,11 @@
           <t>Class 8 (BIO)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
       <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="7" t="inlineStr"/>
@@ -1209,10 +1213,14 @@
       <c r="B24" s="7" t="inlineStr"/>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
       <c r="E24" s="7" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="7" t="inlineStr"/>
@@ -1228,12 +1236,12 @@
       <c r="B25" s="7" t="inlineStr"/>
       <c r="C25" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (BIO)</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr"/>
@@ -1251,14 +1259,10 @@
       <c r="B26" s="7" t="inlineStr"/>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
+          <t>Class 10 (BIO)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="7" t="inlineStr"/>
@@ -1271,17 +1275,13 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Class 10 (BIO)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="7" t="inlineStr"/>
@@ -1294,17 +1294,17 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
           <t>Class 9 (BIO)</t>
         </is>
       </c>
+      <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr"/>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="7" t="inlineStr"/>
@@ -1384,28 +1384,28 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
+      <c r="D32" s="7" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -1425,30 +1425,26 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -1466,26 +1462,26 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -1507,23 +1503,23 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -1549,25 +1545,21 @@
           <t>Class 6 (MATH)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Class 4 (MATH)</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -1584,35 +1576,31 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (MATH)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (MATH)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
+      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -1694,7 +1682,7 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (G.K)</t>
+          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1702,20 +1690,20 @@
           <t>Class 1(A) (MATH)</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
@@ -1732,33 +1720,33 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
@@ -1775,33 +1763,33 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 1(A) (HIN)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (MATH)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 1(A) (G.K)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (TEL)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (MATH)</t>
+          <t>Class 1(A) (MATH)</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -1823,27 +1811,27 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
@@ -1861,33 +1849,33 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (MATH)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (G.K)</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
@@ -1904,33 +1892,33 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (ENG)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>Class 2 (MATH)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr"/>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
@@ -2012,11 +2000,7 @@
       <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
+      <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="7" t="inlineStr"/>
       <c r="I50" s="8" t="inlineStr">
         <is>
@@ -2040,7 +2024,11 @@
           <t>Class 10 (MATH)</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
@@ -2058,19 +2046,15 @@
       <c r="D52" s="7" t="inlineStr"/>
       <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (MATH)</t>
         </is>
       </c>
     </row>
@@ -2087,17 +2071,17 @@
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
     </row>
@@ -2135,15 +2119,19 @@
       <c r="D55" s="7" t="inlineStr"/>
       <c r="E55" s="7" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
     </row>
@@ -2215,29 +2203,33 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr"/>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr"/>
       <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (G.K)</t>
+        </is>
+      </c>
       <c r="I59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2246,29 +2238,29 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr"/>
-      <c r="C60" s="7" t="inlineStr"/>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr"/>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
       <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
+      <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2277,29 +2269,29 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
+      <c r="B61" s="7" t="inlineStr"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (ENG)</t>
+          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr"/>
       <c r="E61" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
       <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
       <c r="I61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2308,28 +2300,28 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr"/>
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr"/>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr"/>
     </row>
@@ -2339,28 +2331,28 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr"/>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
+      <c r="C63" s="7" t="inlineStr"/>
       <c r="D63" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
+      <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
     </row>
@@ -2372,23 +2364,23 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr"/>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr"/>
@@ -2465,23 +2457,23 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr"/>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (CHEM)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
+          <t>Class 4 (G.K)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
@@ -2490,7 +2482,11 @@
           <t>Class 9 (CHEM)</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -2500,32 +2496,36 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (CHEM)</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (CHEM)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr"/>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -2535,28 +2535,36 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr"/>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (G.K)</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
+          <t>Class 7 (PHY)</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
       <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -2566,13 +2574,13 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (G.K)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -2580,10 +2588,18 @@
           <t>Class 8 (CHEM)</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -2596,33 +2612,29 @@
           <t>Class 10 (CHEM)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
+      <c r="C72" s="7" t="inlineStr"/>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr"/>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (PHY)</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -2635,33 +2647,29 @@
           <t>Class 10 (CHEM)</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>Class 7 (PHY)</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (G.K)</t>
+        </is>
+      </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (CHEM)</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Class 5</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -2741,20 +2749,20 @@
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr"/>
@@ -2768,31 +2776,31 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
-        </is>
-      </c>
+      <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -2806,23 +2814,23 @@
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr"/>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -2843,18 +2851,18 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -2871,28 +2879,28 @@
           <t>FRI</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr"/>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr">
         <is>
           <t>Class 10 (TEL)</t>
@@ -2906,31 +2914,31 @@
           <t>SAT</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr"/>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr"/>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr">
         <is>
           <t>Class 8 (TEL)</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr"/>
@@ -3005,33 +3013,33 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -3048,17 +3056,17 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (EVS)</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (HIN)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -3068,13 +3076,13 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (ORAL)</t>
+          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -3091,37 +3099,37 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (EVS)</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (HIN)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="I88" s="8" t="inlineStr">
@@ -3138,37 +3146,37 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ENG)</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (MATH)</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
@@ -3185,33 +3193,33 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (MATH)</t>
+          <t>UKG (B) (HIN)</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (HIN)</t>
+          <t>UKG (B) (TEL)</t>
         </is>
       </c>
       <c r="I90" s="8" t="inlineStr">
@@ -3228,37 +3236,37 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ORAL)</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (HIN)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
@@ -3342,12 +3350,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr"/>
@@ -3358,12 +3366,12 @@
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (G.K)</t>
+          <t>Class 6 (ENG)</t>
         </is>
       </c>
       <c r="I95" s="8" t="inlineStr">
@@ -3380,33 +3388,29 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr"/>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="I96" s="8" t="inlineStr">
@@ -3426,23 +3430,27 @@
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
@@ -3470,15 +3478,15 @@
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr"/>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -3504,26 +3512,30 @@
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr"/>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr"/>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I99" s="8" t="inlineStr">
@@ -3543,26 +3555,30 @@
           <t>Class 3 (ENG)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr"/>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
           <t>Class 5 (ENG)</t>
         </is>
       </c>
+      <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr"/>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (ENG)</t>
+        </is>
+      </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (ENG)</t>
+          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I100" s="8" t="inlineStr">
@@ -3646,30 +3662,26 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
           <t>LKG (TEL)</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
+      <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3687,28 +3699,28 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr"/>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3726,28 +3738,28 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr"/>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (TEL)</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr"/>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="F106" s="7" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (TEL)</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3765,27 +3777,23 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C107" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr"/>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr"/>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
+      <c r="G107" s="7" t="inlineStr"/>
       <c r="H107" s="7" t="inlineStr"/>
       <c r="I107" s="8" t="inlineStr">
         <is>
@@ -3801,31 +3809,31 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr"/>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr">
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr"/>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="H108" s="7" t="inlineStr">
         <is>
           <t>LKG (TEL)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3944,23 +3952,23 @@
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr"/>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
-      <c r="E113" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr"/>
       <c r="H113" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
@@ -3985,13 +3993,13 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 7 (SOC)</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
@@ -3999,12 +4007,12 @@
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr"/>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
-        </is>
-      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr"/>
       <c r="I114" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4019,33 +4027,29 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
+          <t>Class 6 (SOC)</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr"/>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I115" s="8" t="inlineStr">
@@ -4072,7 +4076,7 @@
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr"/>
@@ -4083,7 +4087,7 @@
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr"/>
@@ -4106,26 +4110,26 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr"/>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr"/>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr"/>
-      <c r="H117" s="7" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
+      <c r="H117" s="7" t="inlineStr"/>
       <c r="I117" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4151,20 +4155,20 @@
       <c r="D118" s="7" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
+      <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4243,13 +4247,17 @@
       <c r="C122" s="7" t="inlineStr"/>
       <c r="D122" s="7" t="inlineStr"/>
       <c r="E122" s="7" t="inlineStr"/>
-      <c r="F122" s="7" t="inlineStr"/>
-      <c r="G122" s="7" t="inlineStr"/>
-      <c r="H122" s="7" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
         </is>
       </c>
+      <c r="H122" s="7" t="inlineStr"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
@@ -4266,12 +4274,12 @@
       <c r="C123" s="7" t="inlineStr"/>
       <c r="D123" s="7" t="inlineStr"/>
       <c r="E123" s="7" t="inlineStr"/>
-      <c r="F123" s="7" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr"/>
+      <c r="G123" s="7" t="inlineStr">
         <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="7" t="inlineStr"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
@@ -4291,18 +4299,18 @@
       <c r="E124" s="7" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (HIN)</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr"/>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr"/>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
-      <c r="I124" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4318,14 +4326,14 @@
       <c r="E125" s="7" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 9 (HIN)</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr"/>
       <c r="H125" s="7" t="inlineStr"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4341,18 +4349,18 @@
       <c r="E126" s="7" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (HIN)</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4366,14 +4374,10 @@
       <c r="C127" s="7" t="inlineStr"/>
       <c r="D127" s="7" t="inlineStr"/>
       <c r="E127" s="7" t="inlineStr"/>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr"/>
+      <c r="G127" s="7" t="inlineStr">
         <is>
           <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr"/>
@@ -4451,38 +4455,38 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr"/>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
+      <c r="E131" s="7" t="inlineStr"/>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F131" s="7" t="inlineStr"/>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="H131" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="I131" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+      <c r="I131" s="7" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -4492,40 +4496,40 @@
       </c>
       <c r="B132" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F132" s="7" t="inlineStr"/>
-      <c r="G132" s="7" t="inlineStr">
+      <c r="H132" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="I132" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+      <c r="I132" s="7" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -4533,10 +4537,14 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr"/>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (BIO)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -4546,25 +4554,25 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="F133" s="7" t="inlineStr"/>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H133" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="I133" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+      <c r="I133" s="7" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -4574,36 +4582,36 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (G.K)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr"/>
-      <c r="E134" s="7" t="inlineStr">
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>Class 7 (BIO)</t>
         </is>
       </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr"/>
-      <c r="I134" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+      <c r="I134" s="7" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
@@ -4613,40 +4621,40 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr"/>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="I135" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+      <c r="I135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -4656,7 +4664,7 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -4666,30 +4674,30 @@
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr"/>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>Class 5</t>
-        </is>
-      </c>
+      <c r="I136" s="7" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -4769,22 +4777,18 @@
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr"/>
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
+      <c r="G140" s="7" t="inlineStr"/>
       <c r="H140" s="7" t="inlineStr"/>
       <c r="I140" s="8" t="inlineStr">
         <is>
@@ -4800,31 +4804,31 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (G.K)</t>
-        </is>
-      </c>
-      <c r="C141" s="7" t="inlineStr">
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr"/>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr"/>
+      <c r="H141" s="7" t="inlineStr">
         <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr"/>
-      <c r="E141" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="inlineStr"/>
       <c r="I141" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -4837,28 +4841,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (HIN)</t>
-        </is>
-      </c>
+      <c r="B142" s="7" t="inlineStr"/>
       <c r="C142" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (HIN)</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr"/>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="F142" s="7" t="inlineStr"/>
+      <c r="G142" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr"/>
       <c r="H142" s="7" t="inlineStr"/>
       <c r="I142" s="8" t="inlineStr">
         <is>
@@ -4880,19 +4884,15 @@
       <c r="C143" s="7" t="inlineStr"/>
       <c r="D143" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="E143" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
+      <c r="F143" s="7" t="inlineStr"/>
       <c r="G143" s="7" t="inlineStr"/>
       <c r="H143" s="7" t="inlineStr"/>
       <c r="I143" s="8" t="inlineStr">
@@ -4912,24 +4912,24 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
+      <c r="C144" s="7" t="inlineStr"/>
       <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr"/>
-      <c r="H144" s="7" t="inlineStr"/>
+      <c r="H144" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="I144" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -4947,24 +4947,28 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr"/>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr"/>
-      <c r="E145" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
       <c r="G145" s="7" t="inlineStr"/>
-      <c r="H145" s="7" t="inlineStr"/>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
       <c r="I145" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -5040,13 +5044,17 @@
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr"/>
-      <c r="C149" s="7" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr"/>
+      <c r="D149" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr"/>
-      <c r="E149" s="7" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="F149" s="7" t="inlineStr"/>
       <c r="G149" s="7" t="inlineStr"/>
       <c r="H149" s="7" t="inlineStr"/>
@@ -5059,11 +5067,7 @@
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr"/>
-      <c r="C150" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+      <c r="C150" s="7" t="inlineStr"/>
       <c r="D150" s="7" t="inlineStr">
         <is>
           <t>Class 10 (PHY)</t>
@@ -5081,12 +5085,12 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B151" s="7" t="inlineStr"/>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr"/>
       <c r="D151" s="7" t="inlineStr"/>
       <c r="E151" s="7" t="inlineStr"/>
       <c r="F151" s="7" t="inlineStr"/>
@@ -5103,11 +5107,7 @@
       <c r="B152" s="7" t="inlineStr"/>
       <c r="C152" s="7" t="inlineStr"/>
       <c r="D152" s="7" t="inlineStr"/>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="E152" s="7" t="inlineStr"/>
       <c r="F152" s="7" t="inlineStr"/>
       <c r="G152" s="7" t="inlineStr"/>
       <c r="H152" s="7" t="inlineStr"/>
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B153" s="7" t="inlineStr"/>
       <c r="C153" s="7" t="inlineStr"/>
-      <c r="D153" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr"/>
+      <c r="D153" s="7" t="inlineStr"/>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="F153" s="7" t="inlineStr"/>
       <c r="G153" s="7" t="inlineStr"/>
       <c r="H153" s="7" t="inlineStr"/>
@@ -5145,7 +5145,11 @@
           <t>Class 10 (PHY)</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr"/>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="F154" s="7" t="inlineStr"/>
       <c r="G154" s="7" t="inlineStr"/>
       <c r="H154" s="7" t="inlineStr"/>
@@ -5221,37 +5225,37 @@
       </c>
       <c r="B158" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
         </is>
       </c>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="inlineStr">
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="I158" s="8" t="inlineStr">
@@ -5268,37 +5272,33 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
           <t>LKG (ENG)</t>
         </is>
       </c>
-      <c r="D159" s="7" t="inlineStr">
+      <c r="E159" s="7" t="inlineStr"/>
+      <c r="F159" s="7" t="inlineStr">
         <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="E159" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
       <c r="G159" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr">
         <is>
-          <t>LKG (ORAL)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
@@ -5315,37 +5315,33 @@
       </c>
       <c r="B160" s="7" t="inlineStr">
         <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr"/>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
           <t>LKG (MATH)</t>
         </is>
       </c>
-      <c r="C160" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="D160" s="7" t="inlineStr">
+      <c r="G160" s="7" t="inlineStr">
         <is>
           <t>LKG (MATH)</t>
         </is>
       </c>
-      <c r="E160" s="7" t="inlineStr">
+      <c r="H160" s="7" t="inlineStr">
         <is>
           <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="G160" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="I160" s="8" t="inlineStr">
@@ -5362,33 +5358,37 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
+          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>LKG (ORAL)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr"/>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
       <c r="G161" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="H161" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I161" s="8" t="inlineStr">
@@ -5415,18 +5415,22 @@
       </c>
       <c r="D162" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="E162" s="7" t="inlineStr"/>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
           <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -5453,12 +5457,12 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="E163" s="7" t="inlineStr"/>
@@ -5469,12 +5473,12 @@
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>LKG (ORAL)</t>
+          <t>Class 2 (HIN)</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (HIN)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I163" s="8" t="inlineStr">
@@ -5560,12 +5564,12 @@
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="G167" s="7" t="inlineStr"/>
+      <c r="H167" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="H167" s="7" t="inlineStr"/>
       <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
@@ -5584,13 +5588,13 @@
       <c r="E168" s="7" t="inlineStr"/>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr"/>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -5636,17 +5640,17 @@
       <c r="C170" s="7" t="inlineStr"/>
       <c r="D170" s="7" t="inlineStr"/>
       <c r="E170" s="7" t="inlineStr"/>
-      <c r="F170" s="7" t="inlineStr">
+      <c r="F170" s="7" t="inlineStr"/>
+      <c r="G170" s="7" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G170" s="7" t="inlineStr">
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="H170" s="7" t="inlineStr"/>
       <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
@@ -5665,18 +5669,18 @@
       <c r="E171" s="7" t="inlineStr"/>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (SOC)</t>
+          <t>Class 10 (SOC)</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="H171" s="7" t="inlineStr"/>
       <c r="I171" s="8" t="inlineStr">
         <is>
-          <t>Class 8 (SOC)</t>
+          <t>Class 9 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5692,18 +5696,18 @@
       <c r="E172" s="7" t="inlineStr"/>
       <c r="F172" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr"/>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="G172" s="7" t="inlineStr">
+      <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="inlineStr"/>
-      <c r="I172" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5777,30 +5781,26 @@
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr"/>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="C176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E176" s="7" t="inlineStr"/>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
+          <t>Class 1(B) (G.K)</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="8" t="inlineStr">
         <is>
@@ -5819,26 +5819,26 @@
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
+      <c r="C177" s="7" t="inlineStr"/>
       <c r="D177" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr"/>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
+          <t>Class 1(B) (HIN)</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr"/>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (G.K)</t>
+          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="I177" s="8" t="inlineStr">
@@ -5855,29 +5855,29 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr"/>
       <c r="D178" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E178" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr"/>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (TEL)</t>
+          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="I178" s="8" t="inlineStr">
@@ -5894,28 +5894,28 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="D179" s="7" t="inlineStr"/>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="E179" s="7" t="inlineStr"/>
+      <c r="F179" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
+          <t>Class 1(B) (G.K)</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr"/>
@@ -5933,31 +5933,31 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="D180" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="D180" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr"/>
       <c r="F180" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr"/>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="H180" s="7" t="inlineStr"/>
       <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Class 1(B)</t>
@@ -5972,27 +5972,31 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (G.K)</t>
-        </is>
-      </c>
-      <c r="C181" s="7" t="inlineStr"/>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
       <c r="D181" s="7" t="inlineStr"/>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (HIN)</t>
+          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr"/>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr"/>
       <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Class 1(B)</t>
@@ -6068,28 +6072,24 @@
         </is>
       </c>
       <c r="B185" s="7" t="inlineStr"/>
-      <c r="C185" s="7" t="inlineStr"/>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (COMP)</t>
+        </is>
+      </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (COMP)</t>
         </is>
       </c>
-      <c r="E185" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="F185" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
+      <c r="F185" s="7" t="inlineStr"/>
       <c r="G185" s="7" t="inlineStr"/>
-      <c r="H185" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="H185" s="7" t="inlineStr"/>
       <c r="I185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
@@ -6101,21 +6101,25 @@
       <c r="B186" s="7" t="inlineStr"/>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 1(A) (COMP)</t>
         </is>
       </c>
       <c r="D186" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
-      <c r="G186" s="7" t="inlineStr"/>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (COMP)</t>
+        </is>
+      </c>
       <c r="H186" s="7" t="inlineStr"/>
       <c r="I186" s="7" t="inlineStr"/>
     </row>
@@ -6127,30 +6131,22 @@
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr"/>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (COMP)</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (COMP)</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="inlineStr"/>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (COMP)</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
+      <c r="F187" s="7" t="inlineStr"/>
+      <c r="G187" s="7" t="inlineStr"/>
       <c r="H187" s="7" t="inlineStr"/>
       <c r="I187" s="7" t="inlineStr"/>
     </row>
@@ -6160,23 +6156,27 @@
           <t>THU</t>
         </is>
       </c>
-      <c r="B188" s="7" t="inlineStr"/>
-      <c r="C188" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr"/>
       <c r="D188" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
+          <t>Class 6 (COMP)</t>
         </is>
       </c>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr"/>
+          <t>Class 1(A) (COMP)</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (COMP)</t>
+        </is>
+      </c>
       <c r="G188" s="7" t="inlineStr"/>
       <c r="H188" s="7" t="inlineStr"/>
       <c r="I188" s="7" t="inlineStr"/>
@@ -6190,20 +6190,20 @@
       <c r="B189" s="7" t="inlineStr"/>
       <c r="C189" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (COMP)</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="inlineStr"/>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
+      <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr"/>
       <c r="H189" s="7" t="inlineStr"/>
       <c r="I189" s="7" t="inlineStr"/>
@@ -6217,21 +6217,25 @@
       <c r="B190" s="7" t="inlineStr"/>
       <c r="C190" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr"/>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (COMP)</t>
         </is>
       </c>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (COMP)</t>
-        </is>
-      </c>
-      <c r="E190" s="7" t="inlineStr"/>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
-      <c r="G190" s="7" t="inlineStr"/>
       <c r="H190" s="7" t="inlineStr"/>
       <c r="I190" s="7" t="inlineStr"/>
     </row>
@@ -6310,12 +6314,12 @@
       <c r="F194" s="7" t="inlineStr"/>
       <c r="G194" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (P.E.T)</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (P.E.T)</t>
         </is>
       </c>
       <c r="I194" s="7" t="inlineStr"/>
@@ -6333,12 +6337,12 @@
       <c r="F195" s="7" t="inlineStr"/>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (P.E.T)</t>
+          <t>Class 7 (P.E.T)</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
+          <t>Class 3 (P.E.T)</t>
         </is>
       </c>
       <c r="I195" s="7" t="inlineStr"/>
@@ -6356,12 +6360,12 @@
       <c r="F196" s="7" t="inlineStr"/>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (P.E.T)</t>
+          <t>LKG (P.E.T)</t>
         </is>
       </c>
       <c r="I196" s="7" t="inlineStr"/>
@@ -6379,7 +6383,7 @@
       <c r="F197" s="7" t="inlineStr"/>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (P.E.T)</t>
+          <t>Class 2 (P.E.T)</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr"/>
@@ -6403,7 +6407,7 @@
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (P.E.T)</t>
+          <t>Class 8 (P.E.T)</t>
         </is>
       </c>
       <c r="I198" s="7" t="inlineStr"/>
@@ -6421,12 +6425,12 @@
       <c r="F199" s="7" t="inlineStr"/>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>LKG (P.E.T)</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (P.E.T)</t>
+          <t>Class 9 (P.E.T)</t>
         </is>
       </c>
       <c r="I199" s="7" t="inlineStr"/>
@@ -6739,19 +6743,19 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -6763,7 +6767,7 @@
       <c r="G2" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -6786,7 +6790,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
@@ -6804,8 +6808,8 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>K.ESWAR
+(PHY)</t>
         </is>
       </c>
       <c r="O2" s="7" t="inlineStr">
@@ -6828,56 +6832,56 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K3" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -6898,10 +6902,9 @@
 (BIO)</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
+      <c r="O3" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -6919,19 +6922,19 @@
       <c r="C4" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -6948,54 +6951,56 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(G.K)</t>
+          <t>N.NAVYA
+(ENG)</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
       <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O4" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -7006,74 +7011,73 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>ANURADHA
 (EVS)</t>
         </is>
       </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>SHEKINA
+(HIN)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
       <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
@@ -7082,9 +7086,10 @@
 (ENG)</t>
         </is>
       </c>
-      <c r="P5" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -7096,31 +7101,31 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -7131,44 +7136,44 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>S.GAYATHRI
+(MATH)</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>K.ESWAR
+(G.K)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
       <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
@@ -7186,85 +7191,85 @@
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
       <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
       <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -7276,61 +7281,61 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(HIN)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
 (EVS)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
+          <t>D.SUMANI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -7341,20 +7346,20 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7420,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (CLASS)</t>
         </is>
       </c>
@@ -7462,25 +7467,25 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -7497,22 +7502,22 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -7525,21 +7530,22 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7557,7 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -7568,22 +7574,22 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
           <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
@@ -7592,44 +7598,43 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
       <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7646,7 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -7653,13 +7658,13 @@
       <c r="E12" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(HIN)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -7676,44 +7681,43 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
+      <c r="N12" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
@@ -7730,14 +7734,14 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -7748,20 +7752,20 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
           <t>ANURADHA
 (EVS)</t>
         </is>
       </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -7772,37 +7776,38 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr">
@@ -7819,7 +7824,7 @@
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -7831,25 +7836,25 @@
       <c r="E14" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>ANURADHA
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(G.K)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -7860,16 +7865,16 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
@@ -7878,26 +7883,26 @@
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -7909,79 +7914,79 @@
       <c r="C15" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -7998,86 +8003,86 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
           <t>SHEKINA
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
 (HIN)</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8143,7 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (CLASS)</t>
         </is>
       </c>
@@ -8185,31 +8190,31 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (MATH)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -8226,20 +8231,20 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
-(G.K)</t>
+(SOC)</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -8250,8 +8255,8 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
@@ -8262,8 +8267,8 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -8281,19 +8286,19 @@
       <c r="D19" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -8304,56 +8309,55 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>N.NAVYA
+(ENG)</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
       <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8365,31 +8369,31 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -8412,37 +8416,37 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="P20" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8460,13 +8464,13 @@
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -8478,60 +8482,59 @@
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(HIN)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="N21" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="O21" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="P21" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -8543,13 +8546,13 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -8560,62 +8563,62 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>CHANDRAKALA
+(G.K)</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
-(MATH)</t>
+          <t>S.GAYATHRI
+(EVS)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
@@ -8633,73 +8636,73 @@
       <c r="C23" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
       <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="O23" s="7" t="inlineStr">
@@ -8710,8 +8713,8 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>D.GOWTHAM
-(MATH)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
     </row>
@@ -8722,74 +8725,74 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="M24" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
@@ -8862,7 +8865,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (CLASS)</t>
         </is>
       </c>
@@ -8886,16 +8889,16 @@
       </c>
       <c r="O25" s="8" t="inlineStr">
         <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
           <t>D.GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -8909,19 +8912,19 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (ENG)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -8933,7 +8936,7 @@
       <c r="G26" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -8957,7 +8960,7 @@
       <c r="K26" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(G.K)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -8974,14 +8977,14 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
@@ -8999,49 +9002,49 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (MATH)</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -9052,8 +9055,8 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -9062,22 +9065,21 @@
 (SOC)</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9089,19 +9091,19 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -9112,60 +9114,62 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>ANURADHA
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="M28" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
+(G.K)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="O28" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P28" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9181,7 @@
       <c r="C29" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -9189,21 +9193,21 @@
       <c r="E29" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>ANURADHA
 (EVS)</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
@@ -9212,32 +9216,32 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(BIO)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -9246,16 +9250,14 @@
 (CHEM)</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9266,86 +9268,86 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
       <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -9356,40 +9358,40 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
@@ -9398,16 +9400,16 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
@@ -9422,20 +9424,20 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="P31" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9447,19 +9449,19 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (TEL)</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -9522,9 +9524,10 @@
 (MATH)</t>
         </is>
       </c>
-      <c r="P32" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9588,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (CLASS)</t>
         </is>
       </c>
@@ -9609,16 +9612,16 @@
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
           <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -9638,51 +9641,51 @@
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -9697,14 +9700,13 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="O34" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
@@ -9728,51 +9730,51 @@
       <c r="D35" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -9781,26 +9783,24 @@
       </c>
       <c r="M35" s="7" t="inlineStr">
         <is>
-          <t>SAI KEERTHI
-(HIN)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="O35" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="P35" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>Recreation</t>
         </is>
       </c>
     </row>
@@ -9812,84 +9812,85 @@
       <c r="C36" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(G.K)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="O36" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="O36" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>SAIRAM
-(PHY)</t>
+          <t>CHALAPATHI
+(BIO)</t>
         </is>
       </c>
     </row>
@@ -9900,78 +9901,79 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="M37" s="7" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
           <t>Recreation</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
@@ -9989,85 +9991,85 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (PHY)</t>
         </is>
       </c>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10081,7 @@
       <c r="C39" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -10097,33 +10099,33 @@
       <c r="F39" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
@@ -10132,32 +10134,32 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>N.NAVYA
+(ENG)</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(BIO)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="O39" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="P39" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -10168,74 +10170,74 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="M40" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr">
@@ -10308,7 +10310,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (CLASS)</t>
         </is>
       </c>
@@ -10326,16 +10328,16 @@
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="O41" s="8" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="O41" s="8" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
       <c r="P41" s="8" t="inlineStr">
         <is>
           <t>D.GOWTHAM
@@ -10367,19 +10369,19 @@
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(G.K)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -10402,32 +10404,32 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="M42" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="N42" s="7" t="inlineStr">
+      <c r="O42" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="O42" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
@@ -10445,83 +10447,85 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (EVS)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="N43" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P43" s="7" t="inlineStr">
+      <c r="O43" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
         </is>
       </c>
     </row>
@@ -10533,79 +10537,79 @@
       <c r="C44" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
 (EVS)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M44" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="N44" s="7" t="inlineStr">
+      <c r="O44" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O44" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
@@ -10635,71 +10639,71 @@
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>ANURADHA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J45" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
           <t>Recreation</t>
         </is>
       </c>
-      <c r="O45" s="12" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
         <is>
           <t>Recreation</t>
-        </is>
-      </c>
-      <c r="P45" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -10717,39 +10721,39 @@
       <c r="D46" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>ANURADHA
-(EVS)</t>
-        </is>
-      </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(G.K)</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
@@ -10758,38 +10762,38 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="M46" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="M46" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
       <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O46" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="O46" s="7" t="inlineStr">
+      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="P46" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -10800,8 +10804,8 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ORAL)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -10813,25 +10817,25 @@
       <c r="E47" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(TEL)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>SHEKINA
+(HIN)</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -10842,44 +10846,44 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr">
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -10890,86 +10894,86 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="P48" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -11030,7 +11034,7 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>K.ESWAR
 (CLASS)</t>
         </is>
       </c>
@@ -11054,14 +11058,14 @@
       </c>
       <c r="O49" s="8" t="inlineStr">
         <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="P49" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
         </is>
       </c>
     </row>

--- a/NRHS/Output/NRHS_Timetable_Final.xlsx
+++ b/NRHS/Output/NRHS_Timetable_Final.xlsx
@@ -653,28 +653,28 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (EVS)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (EVS)</t>
+          <t>UKG (A) (HIN)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (MATH)</t>
+          <t>UKG (A) (TEL)</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -701,22 +701,22 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (HIN)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ENG)</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ORAL)</t>
+          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -738,33 +738,37 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (HIN)</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (HIN)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -781,27 +785,27 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (EVS)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (MATH)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr"/>
@@ -824,34 +828,30 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ENG)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (ORAL)</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (EVS)</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (TEL)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (EVS)</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ORAL)</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
+      <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr">
         <is>
           <t>UKG (A) (HIN)</t>
@@ -871,37 +871,37 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (EVS)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>UKG (A) (TEL)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (ORAL)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (TEL)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
-        </is>
-      </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>UKG (A) (ENG)</t>
+          <t>UKG (A) (MATH)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
+          <t>UKG (A) (MATH)</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>UKG (A) (HIN)</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>UKG (A) (ENG)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr"/>
@@ -977,7 +977,7 @@
       <c r="B14" s="7" t="inlineStr"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (BIO)</t>
+          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1000,12 +1000,12 @@
       <c r="B15" s="7" t="inlineStr"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -1023,12 +1023,12 @@
       <c r="B16" s="7" t="inlineStr"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (BIO)</t>
+          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (BIO)</t>
+          <t>Class 10 (BIO)</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (BIO)</t>
+          <t>Class 9 (BIO)</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       <c r="B19" s="7" t="inlineStr"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (BIO)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (BIO)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (BIO)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr"/>
@@ -1182,23 +1182,23 @@
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (MATH)</t>
+          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (MATH)</t>
+          <t>Class 5 (MATH)</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -1220,30 +1220,26 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Class 7</t>
@@ -1261,15 +1257,15 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1302,25 +1298,21 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (MATH)</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
+      <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="7" t="inlineStr"/>
       <c r="I26" s="8" t="inlineStr">
         <is>
@@ -1339,26 +1331,30 @@
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr"/>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
@@ -1375,31 +1371,35 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (MATH)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (MATH)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (MATH)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (MATH)</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (MATH)</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (MATH)</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (MATH)</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (MATH)</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (MATH)</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1472,23 +1472,23 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (HIN)</t>
+          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -1515,32 +1515,28 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (ENG)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (EVS)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (G.K)</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -1572,18 +1568,22 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (TEL)</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (EVS)</t>
+          <t>Class 2 (MATH)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -1605,19 +1605,19 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (MATH)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
-        </is>
-      </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (G.K)</t>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (EVS)</t>
+          <t>Class 1(A) (ENG)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -1648,32 +1648,32 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (G.K)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -1695,32 +1695,32 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>Class 1(A) (MATH)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (TEL)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (EVS)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(A) (HIN)</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
           <t>Class 1(A) (ENG)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (MATH)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (ENG)</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (HIN)</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (EVS)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(A) (TEL)</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -1857,19 +1857,15 @@
       <c r="D43" s="7" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
-        </is>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
     </row>
@@ -1889,10 +1885,14 @@
           <t>Class 9 (MATH)</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (MATH)</t>
+        </is>
+      </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>Class 9 (MATH)</t>
+          <t>Class 10 (MATH)</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (MATH)</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
           <t>Class 9 (MATH)</t>
-        </is>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (MATH)</t>
         </is>
       </c>
     </row>
@@ -2014,27 +2014,23 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (ENG)</t>
-        </is>
-      </c>
+      <c r="B50" s="7" t="inlineStr"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (G.K)</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr">
         <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
+      <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
@@ -2051,15 +2047,15 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (ENG)</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
@@ -2067,14 +2063,10 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
+      <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
     </row>
@@ -2086,10 +2078,14 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (ENG)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr"/>
       <c r="D52" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
@@ -2097,16 +2093,20 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2117,23 +2117,23 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (ENG)</t>
+          <t>Class 9 (ENG)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr"/>
       <c r="D53" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (ENG)</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
@@ -2148,18 +2148,18 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (ENG)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (ENG)</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr"/>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (ENG)</t>
+          <t>Class 7 (ENG)</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -2167,11 +2167,7 @@
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (ENG)</t>
-        </is>
-      </c>
+      <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="7" t="inlineStr"/>
       <c r="I54" s="7" t="inlineStr"/>
     </row>
@@ -2186,23 +2182,27 @@
           <t>Class 10 (ENG)</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr"/>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Class 9 (ENG)</t>
         </is>
       </c>
+      <c r="D55" s="7" t="inlineStr"/>
       <c r="E55" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (ENG)</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (ENG)</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>Class 7 (ENG)</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr"/>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
     </row>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (PHY)</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (PHY)</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (PHY)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -2319,30 +2319,30 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (CHEM)</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (EVS)</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>Class 8 (PHY)</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (G.K)</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Class 9 (CHEM)</t>
@@ -2362,37 +2362,33 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (CHEM)</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (G.K)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (PHY)</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (PHY)</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -2409,28 +2405,32 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (G.K)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (CHEM)</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (CHEM)</t>
-        </is>
-      </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (PHY)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (G.K)</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
           <t>Class 7 (PHY)</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr"/>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (G.K)</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -2452,33 +2452,33 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (CHEM)</t>
+          <t>Class 9 (CHEM)</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (CHEM)</t>
+          <t>Class 6 (CHEM)</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (G.K)</t>
+          <t>Class 10 (CHEM)</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (G.K)</t>
+          <t>Class 8 (PHY)</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (CHEM)</t>
+          <t>Class 5 (EVS)</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (EVS)</t>
+          <t>Class 7 (CHEM)</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -2495,33 +2495,33 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (PHY)</t>
+          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (G.K)</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (G.K)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (CHEM)</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (EVS)</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (CHEM)</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (CHEM)</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (EVS)</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (G.K)</t>
-        </is>
-      </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (CHEM)</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr"/>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
@@ -2631,31 +2631,31 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (TEL)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
+      <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2666,28 +2666,28 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (TEL)</t>
+          <t>Class 9 (TEL)</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr"/>
@@ -2701,28 +2701,28 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (TEL)</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (TEL)</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr"/>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (TEL)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (TEL)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr"/>
@@ -2736,28 +2736,28 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (TEL)</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (TEL)</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>Class 9 (TEL)</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (TEL)</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>Class 7 (TEL)</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (TEL)</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr"/>
@@ -2776,13 +2776,13 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (TEL)</t>
+          <t>Class 10 (TEL)</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr"/>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (TEL)</t>
+          <t>Class 7 (TEL)</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -2790,12 +2790,12 @@
           <t>Class 6 (TEL)</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (TEL)</t>
-        </is>
-      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (TEL)</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (MATH)</t>
+          <t>UKG (B) (EVS)</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (MATH)</t>
+          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -2883,22 +2883,22 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (TEL)</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (HIN)</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
@@ -2915,30 +2915,34 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ENG)</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (HIN)</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (EVS)</t>
@@ -2958,33 +2962,37 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (EVS)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ENG)</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="I79" s="8" t="inlineStr">
@@ -3006,32 +3014,28 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (ORAL)</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (EVS)</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (TEL)</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
@@ -3053,7 +3057,7 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (ENG)</t>
+          <t>UKG (B) (ORAL)</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -3074,7 +3078,7 @@
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>UKG (B) (ORAL)</t>
+          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
@@ -3091,37 +3095,33 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
+          <t>UKG (B) (HIN)</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
           <t>UKG (B) (ENG)</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (MATH)</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>UKG (B) (EVS)</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (TEL)</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (HIN)</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>UKG (B) (ORAL)</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (EVS)</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (ENG)</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>UKG (B) (MATH)</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr"/>
@@ -3201,28 +3201,28 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (ENG)</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
         </is>
       </c>
       <c r="I86" s="8" t="inlineStr">
@@ -3244,28 +3244,28 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (ENG)</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
         </is>
       </c>
       <c r="I87" s="8" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (ENG)</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr"/>
@@ -3330,20 +3330,20 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr"/>
+          <t>Class 4 (ENG)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (ENG)</t>
-        </is>
-      </c>
+      <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="8" t="inlineStr">
@@ -3365,25 +3365,25 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (ENG)</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr"/>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (ENG)</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
+      <c r="G90" s="7" t="inlineStr"/>
       <c r="H90" s="7" t="inlineStr">
         <is>
           <t>Class 6 (ENG)</t>
@@ -3408,17 +3408,17 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (ENG)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (ENG)</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (ENG)</t>
-        </is>
-      </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (ENG)</t>
+          <t>Class 2 (ENG)</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (ENG)</t>
+          <t>Class 4 (ENG)</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr"/>
@@ -3504,26 +3504,30 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr"/>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr">
         <is>
@@ -3547,23 +3551,23 @@
           <t>LKG (TEL)</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr"/>
       <c r="I96" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3583,25 +3587,25 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>LKG (TEL)</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (TEL)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="8" t="inlineStr">
         <is>
@@ -3617,30 +3621,30 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
+          <t>Class 2 (TEL)</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>Class 3 (TEL)</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (TEL)</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>LKG (TEL)</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr"/>
       <c r="H98" s="7" t="inlineStr"/>
       <c r="I98" s="8" t="inlineStr">
         <is>
@@ -3659,12 +3663,12 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>LKG (TEL)</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr"/>
       <c r="E99" s="7" t="inlineStr">
         <is>
           <t>Class 4 (TEL)</t>
@@ -3672,15 +3676,15 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (TEL)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr">
         <is>
           <t>Class 2</t>
@@ -3698,28 +3702,24 @@
           <t>Class 2 (TEL)</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (TEL)</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Class 5 (TEL)</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>LKG (TEL)</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (TEL)</t>
+          <t>Class 3 (TEL)</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (TEL)</t>
-        </is>
-      </c>
+      <c r="H100" s="7" t="inlineStr"/>
       <c r="I100" s="7" t="inlineStr"/>
     </row>
     <row r="102">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr"/>
@@ -3808,15 +3808,15 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (SOC)</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr"/>
       <c r="I104" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -3831,31 +3831,31 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
+          <t>Class 5 (SOC)</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr"/>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr"/>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (SOC)</t>
-        </is>
-      </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr">
         <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="H105" s="7" t="inlineStr"/>
       <c r="I105" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -3873,28 +3873,28 @@
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C106" s="7" t="inlineStr"/>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>Class 7 (SOC)</t>
         </is>
       </c>
+      <c r="D106" s="7" t="inlineStr"/>
       <c r="E106" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
+      <c r="H106" s="7" t="inlineStr"/>
       <c r="I106" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -3914,23 +3914,23 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (SOC)</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (SOC)</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (SOC)</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (SOC)</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="inlineStr">
+      <c r="G107" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr"/>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr"/>
@@ -3951,28 +3951,28 @@
           <t>Class 6 (SOC)</t>
         </is>
       </c>
-      <c r="C108" s="7" t="inlineStr"/>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (SOC)</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>Class 5 (SOC)</t>
         </is>
       </c>
-      <c r="E108" s="7" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (SOC)</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
         <is>
           <t>Class 3 (SOC)</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (SOC)</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (SOC)</t>
-        </is>
-      </c>
+      <c r="H108" s="7" t="inlineStr"/>
       <c r="I108" s="8" t="inlineStr">
         <is>
           <t>Class 6</t>
@@ -4003,13 +4003,13 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (SOC)</t>
+          <t>Class 4 (SOC)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (SOC)</t>
+          <t>Class 5 (SOC)</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr"/>
@@ -4092,11 +4092,7 @@
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr"/>
-      <c r="H113" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (HIN)</t>
-        </is>
-      </c>
+      <c r="H113" s="7" t="inlineStr"/>
       <c r="I113" s="8" t="inlineStr">
         <is>
           <t>Class 8 (HIN)</t>
@@ -4115,14 +4111,18 @@
       <c r="E114" s="7" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (HIN)</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr"/>
-      <c r="H114" s="7" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr">
-        <is>
-          <t>Class 8 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4138,18 +4138,14 @@
       <c r="E115" s="7" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (HIN)</t>
-        </is>
-      </c>
+          <t>Class 9 (HIN)</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr"/>
       <c r="H115" s="7" t="inlineStr"/>
       <c r="I115" s="8" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 8 (HIN)</t>
         </is>
       </c>
     </row>
@@ -4192,13 +4188,13 @@
       <c r="E117" s="7" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (HIN)</t>
+          <t>Class 10 (HIN)</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr"/>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (HIN)</t>
+          <t>Class 9 (HIN)</t>
         </is>
       </c>
       <c r="I117" s="8" t="inlineStr">
@@ -4219,11 +4215,15 @@
       <c r="E118" s="7" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (HIN)</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr"/>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (HIN)</t>
         </is>
       </c>
-      <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr"/>
       <c r="I118" s="7" t="inlineStr"/>
     </row>
     <row r="120">
@@ -4296,33 +4296,33 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr"/>
-      <c r="G122" s="7" t="inlineStr">
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr"/>
@@ -4333,31 +4333,35 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr"/>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (BIO)</t>
+        </is>
+      </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (G.K)</t>
+          <t>Class 2 (EVS)</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (BIO)</t>
+          <t>Class 3 (EVS)</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr"/>
@@ -4368,32 +4372,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr"/>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (BIO)</t>
-        </is>
-      </c>
-      <c r="F124" s="7" t="inlineStr"/>
-      <c r="G124" s="7" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
         </is>
       </c>
+      <c r="G124" s="7" t="inlineStr"/>
       <c r="H124" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
@@ -4409,28 +4409,28 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (EVS)</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr"/>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>Class 4 (EVS)</t>
-        </is>
-      </c>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (G.K)</t>
-        </is>
-      </c>
+      <c r="F125" s="7" t="inlineStr"/>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (EVS)</t>
+          <t>Class 3 (MATH)</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr"/>
@@ -4444,28 +4444,28 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (EVS)</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (EVS)</t>
-        </is>
-      </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
           <t>Class 3 (MATH)</t>
         </is>
       </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr"/>
+      <c r="E126" s="7" t="inlineStr"/>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>Class 4 (EVS)</t>
+        </is>
+      </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (EVS)</t>
+          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
@@ -4483,33 +4483,33 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (BIO)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (EVS)</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Class 3 (MATH)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
           <t>Class 4 (EVS)</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (MATH)</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (EVS)</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
+          <t>Class 2 (G.K)</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr"/>
+      <c r="H127" s="7" t="inlineStr">
         <is>
           <t>Class 3 (EVS)</t>
-        </is>
-      </c>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (BIO)</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr"/>
@@ -4587,20 +4587,20 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
+      <c r="C131" s="7" t="inlineStr"/>
       <c r="D131" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr"/>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr"/>
@@ -4625,25 +4625,21 @@
       <c r="C132" s="7" t="inlineStr"/>
       <c r="D132" s="7" t="inlineStr">
         <is>
+          <t>Class 3 (HIN)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>Class 5 (HIN)</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="E132" s="7" t="inlineStr">
-        <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F132" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
       <c r="G132" s="7" t="inlineStr"/>
-      <c r="H132" s="7" t="inlineStr">
-        <is>
-          <t>Class 5 (HIN)</t>
-        </is>
-      </c>
+      <c r="H132" s="7" t="inlineStr"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Class 4</t>
@@ -4656,28 +4652,28 @@
           <t>WED</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr"/>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>Class 4 (HIN)</t>
         </is>
       </c>
+      <c r="C133" s="7" t="inlineStr"/>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 3 (HIN)</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F133" s="7" t="inlineStr"/>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr"/>
       <c r="H133" s="7" t="inlineStr"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
@@ -4693,23 +4689,23 @@
       </c>
       <c r="B134" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr"/>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (HIN)</t>
+          <t>Class 6 (HIN)</t>
         </is>
       </c>
       <c r="E134" s="7" t="inlineStr">
         <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
           <t>Class 3 (HIN)</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr"/>
@@ -4731,20 +4727,20 @@
           <t>Class 4 (HIN)</t>
         </is>
       </c>
-      <c r="C135" s="7" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr"/>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t>Class 6 (HIN)</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="inlineStr"/>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (HIN)</t>
+          <t>Class 5 (HIN)</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr"/>
@@ -4763,26 +4759,30 @@
       </c>
       <c r="B136" s="7" t="inlineStr">
         <is>
+          <t>Class 4 (HIN)</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>Class 7 (HIN)</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr"/>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (HIN)</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
           <t>Class 5 (HIN)</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr"/>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Class 6 (HIN)</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="inlineStr">
-        <is>
-          <t>Class 7 (HIN)</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr">
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>Class 3 (HIN)</t>
         </is>
       </c>
-      <c r="G136" s="7" t="inlineStr"/>
       <c r="H136" s="7" t="inlineStr"/>
       <c r="I136" s="7" t="inlineStr"/>
     </row>
@@ -4878,9 +4878,17 @@
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr"/>
-      <c r="C141" s="7" t="inlineStr"/>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Class 9 (PHY)</t>
+        </is>
+      </c>
       <c r="D141" s="7" t="inlineStr"/>
-      <c r="E141" s="7" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>Class 10 (PHY)</t>
+        </is>
+      </c>
       <c r="F141" s="7" t="inlineStr"/>
       <c r="G141" s="7" t="inlineStr"/>
       <c r="H141" s="7" t="inlineStr"/>
@@ -4894,11 +4902,7 @@
       </c>
       <c r="B142" s="7" t="inlineStr"/>
       <c r="C142" s="7" t="inlineStr"/>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>Class 10 (PHY)</t>
-        </is>
-      </c>
+      <c r="D142" s="7" t="inlineStr"/>
       <c r="E142" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
@@ -4940,11 +4944,7 @@
       </c>
       <c r="B144" s="7" t="inlineStr"/>
       <c r="C144" s="7" t="inlineStr"/>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (PHY)</t>
-        </is>
-      </c>
+      <c r="D144" s="7" t="inlineStr"/>
       <c r="E144" s="7" t="inlineStr">
         <is>
           <t>Class 10 (PHY)</t>
@@ -4962,12 +4962,12 @@
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr"/>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C145" s="7" t="inlineStr"/>
+      <c r="D145" s="7" t="inlineStr">
         <is>
           <t>Class 10 (PHY)</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr"/>
       <c r="E145" s="7" t="inlineStr">
         <is>
           <t>Class 9 (PHY)</t>
@@ -5048,37 +5048,37 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
           <t>LKG (ORAL)</t>
         </is>
       </c>
-      <c r="C149" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
         <is>
           <t>LKG (ENG)</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="E149" s="7" t="inlineStr">
+      <c r="G149" s="7" t="inlineStr">
         <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="F149" s="7" t="inlineStr">
+      <c r="H149" s="7" t="inlineStr">
         <is>
           <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>LKG (EVS)</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="D150" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="E150" s="7" t="inlineStr">
@@ -5121,7 +5121,7 @@
       <c r="G150" s="7" t="inlineStr"/>
       <c r="H150" s="7" t="inlineStr">
         <is>
-          <t>LKG (ORAL)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I150" s="8" t="inlineStr">
@@ -5138,37 +5138,37 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
           <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="C151" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
         </is>
       </c>
       <c r="I151" s="8" t="inlineStr">
@@ -5185,33 +5185,33 @@
       </c>
       <c r="B152" s="7" t="inlineStr">
         <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ENG)</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
           <t>LKG (MATH)</t>
         </is>
       </c>
-      <c r="C152" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="D152" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
+          <t>LKG (EVS)</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
           <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="G152" s="7" t="inlineStr"/>
       <c r="H152" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (ORAL)</t>
         </is>
       </c>
       <c r="I152" s="8" t="inlineStr">
@@ -5228,33 +5228,37 @@
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Class 2 (HIN)</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>LKG (ORAL)</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
           <t>LKG (EVS)</t>
         </is>
       </c>
-      <c r="C153" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
-      <c r="D153" s="7" t="inlineStr">
+      <c r="G153" s="7" t="inlineStr">
         <is>
           <t>LKG (MATH)</t>
         </is>
       </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>LKG (MATH)</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ORAL)</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr"/>
       <c r="H153" s="7" t="inlineStr">
         <is>
-          <t>LKG (MATH)</t>
+          <t>LKG (EVS)</t>
         </is>
       </c>
       <c r="I153" s="8" t="inlineStr">
@@ -5271,19 +5275,19 @@
       </c>
       <c r="B154" s="7" t="inlineStr">
         <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
           <t>LKG (ENG)</t>
         </is>
       </c>
-      <c r="C154" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="D154" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (HIN)</t>
-        </is>
-      </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
           <t>LKG (ORAL)</t>
@@ -5291,17 +5295,13 @@
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>LKG (ENG)</t>
-        </is>
-      </c>
+          <t>LKG (MATH)</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr"/>
       <c r="H154" s="7" t="inlineStr">
         <is>
-          <t>LKG (EVS)</t>
+          <t>LKG (MATH)</t>
         </is>
       </c>
       <c r="I154" s="7" t="inlineStr"/>
@@ -5383,12 +5383,12 @@
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G158" s="7" t="inlineStr"/>
-      <c r="H158" s="7" t="inlineStr">
+      <c r="G158" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
+      <c r="H158" s="7" t="inlineStr"/>
       <c r="I158" s="8" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
@@ -5407,18 +5407,18 @@
       <c r="E159" s="7" t="inlineStr"/>
       <c r="F159" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
         </is>
       </c>
       <c r="H159" s="7" t="inlineStr"/>
       <c r="I159" s="8" t="inlineStr">
         <is>
-          <t>Class 10 (SOC)</t>
+          <t>Class 8 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5434,18 +5434,18 @@
       <c r="E160" s="7" t="inlineStr"/>
       <c r="F160" s="7" t="inlineStr">
         <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr"/>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
           <t>Class 9 (SOC)</t>
         </is>
       </c>
-      <c r="G160" s="7" t="inlineStr">
+      <c r="I160" s="8" t="inlineStr">
         <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="inlineStr"/>
-      <c r="I160" s="8" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5461,18 +5461,18 @@
       <c r="E161" s="7" t="inlineStr"/>
       <c r="F161" s="7" t="inlineStr">
         <is>
+          <t>Class 10 (SOC)</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
           <t>Class 8 (SOC)</t>
         </is>
       </c>
-      <c r="G161" s="7" t="inlineStr"/>
-      <c r="H161" s="7" t="inlineStr">
+      <c r="H161" s="7" t="inlineStr"/>
+      <c r="I161" s="8" t="inlineStr">
         <is>
           <t>Class 9 (SOC)</t>
-        </is>
-      </c>
-      <c r="I161" s="8" t="inlineStr">
-        <is>
-          <t>Class 10 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5488,18 +5488,18 @@
       <c r="E162" s="7" t="inlineStr"/>
       <c r="F162" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr"/>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (SOC)</t>
+        </is>
+      </c>
+      <c r="I162" s="8" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="inlineStr"/>
-      <c r="I162" s="8" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
     </row>
@@ -5515,17 +5515,17 @@
       <c r="E163" s="7" t="inlineStr"/>
       <c r="F163" s="7" t="inlineStr">
         <is>
+          <t>Class 9 (SOC)</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
           <t>Class 10 (SOC)</t>
         </is>
       </c>
-      <c r="G163" s="7" t="inlineStr">
+      <c r="H163" s="7" t="inlineStr">
         <is>
           <t>Class 8 (SOC)</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="inlineStr">
-        <is>
-          <t>Class 9 (SOC)</t>
         </is>
       </c>
       <c r="I163" s="7" t="inlineStr"/>
@@ -5600,33 +5600,33 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (G.K)</t>
+          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="E167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr"/>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="I167" s="8" t="inlineStr">
@@ -5648,28 +5648,28 @@
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (EVS)</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr">
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (HIN)</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (ENG)</t>
         </is>
       </c>
-      <c r="E168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="F168" s="7" t="inlineStr"/>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (HIN)</t>
-        </is>
-      </c>
+      <c r="G168" s="7" t="inlineStr"/>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (G.K)</t>
+          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -5686,33 +5686,33 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (EVS)</t>
+          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (TEL)</t>
+          <t>Class 1(B) (HIN)</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
+          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="E169" s="7" t="inlineStr"/>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (HIN)</t>
+          <t>Class 1(B) (G.K)</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (EVS)</t>
         </is>
       </c>
       <c r="I169" s="8" t="inlineStr">
@@ -5737,12 +5737,12 @@
           <t>Class 1(B) (TEL)</t>
         </is>
       </c>
-      <c r="D170" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (ENG)</t>
-        </is>
-      </c>
-      <c r="E170" s="7" t="inlineStr"/>
+      <c r="D170" s="7" t="inlineStr"/>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (MATH)</t>
+        </is>
+      </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (HIN)</t>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (ENG)</t>
+          <t>Class 1(B) (MATH)</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr"/>
@@ -5768,27 +5768,27 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (MATH)</t>
+          <t>Class 1(B) (HIN)</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (ENG)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (EVS)</t>
         </is>
       </c>
-      <c r="D171" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (HIN)</t>
+          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (TEL)</t>
+          <t>Class 1(B) (ENG)</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr"/>
@@ -5821,23 +5821,23 @@
       </c>
       <c r="D172" s="7" t="inlineStr">
         <is>
+          <t>Class 1(B) (TEL)</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr"/>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>Class 1(B) (G.K)</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
           <t>Class 1(B) (MATH)</t>
         </is>
       </c>
-      <c r="E172" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (MATH)</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr">
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (EVS)</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr"/>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (TEL)</t>
         </is>
       </c>
       <c r="I172" s="7" t="inlineStr"/>
@@ -5910,23 +5910,27 @@
           <t>MON</t>
         </is>
       </c>
-      <c r="B176" s="7" t="inlineStr"/>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
+          <t>Class 3 (COMP)</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr"/>
       <c r="E176" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
-      <c r="F176" s="7" t="inlineStr"/>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Class 6 (COMP)</t>
+        </is>
+      </c>
       <c r="G176" s="7" t="inlineStr"/>
       <c r="H176" s="7" t="inlineStr"/>
       <c r="I176" s="7" t="inlineStr"/>
@@ -5937,11 +5941,7 @@
           <t>TUE</t>
         </is>
       </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>Class 8 (COMP)</t>
-        </is>
-      </c>
+      <c r="B177" s="7" t="inlineStr"/>
       <c r="C177" s="7" t="inlineStr">
         <is>
           <t>Class 3 (COMP)</t>
@@ -5949,20 +5949,16 @@
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="inlineStr"/>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>Class 1(B) (COMP)</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr">
+          <t>Class 7 (COMP)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
+      <c r="F177" s="7" t="inlineStr"/>
+      <c r="G177" s="7" t="inlineStr"/>
       <c r="H177" s="7" t="inlineStr"/>
       <c r="I177" s="7" t="inlineStr"/>
     </row>
@@ -5979,21 +5975,25 @@
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>Class 3 (COMP)</t>
-        </is>
-      </c>
-      <c r="D178" s="7" t="inlineStr"/>
+          <t>Class 2 (COMP)</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Class 8 (COMP)</t>
+        </is>
+      </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
           <t>Class 1(B) (COMP)</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr"/>
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>Class 1(A) (COMP)</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr"/>
       <c r="H178" s="7" t="inlineStr"/>
       <c r="I178" s="7" t="inlineStr"/>
     </row>
@@ -6006,17 +6006,17 @@
       <c r="B179" s="7" t="inlineStr"/>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 1(B) (COMP)</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>Class 1(B) (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
@@ -6033,17 +6033,17 @@
       <c r="B180" s="7" t="inlineStr"/>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (COMP)</t>
+          <t>Class 7 (COMP)</t>
         </is>
       </c>
       <c r="D180" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (COMP)</t>
+          <t>Class 4 (COMP)</t>
         </is>
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
+          <t>Class 2 (COMP)</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
@@ -6060,17 +6060,17 @@
       <c r="B181" s="7" t="inlineStr"/>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>Class 7 (COMP)</t>
+          <t>Class 5 (COMP)</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (COMP)</t>
+          <t>Class 6 (COMP)</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (COMP)</t>
+          <t>Class 1(B) (COMP)</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Class 1(A) (P.E.T)</t>
+          <t>Class 9 (P.E.T)</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr"/>
@@ -6176,12 +6176,12 @@
       <c r="F186" s="7" t="inlineStr"/>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (P.E.T)</t>
+          <t>Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>Class 6 (P.E.T)</t>
+          <t>Class 7 (P.E.T)</t>
         </is>
       </c>
       <c r="I186" s="7" t="inlineStr"/>
@@ -6199,12 +6199,12 @@
       <c r="F187" s="7" t="inlineStr"/>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>Class 9 (P.E.T)</t>
+          <t>Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="I187" s="7" t="inlineStr"/>
@@ -6222,7 +6222,7 @@
       <c r="F188" s="7" t="inlineStr"/>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>Class 1(A) (P.E.T)</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr"/>
@@ -6241,12 +6241,12 @@
       <c r="F189" s="7" t="inlineStr"/>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>Class 2 (P.E.T)</t>
+          <t>Class 9 (P.E.T)</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
+          <t>Class 1(A) (P.E.T)</t>
         </is>
       </c>
       <c r="I189" s="7" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
       <c r="F190" s="7" t="inlineStr"/>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>Class 2 (P.E.T)</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
@@ -6581,7 +6581,7 @@
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -6593,25 +6593,25 @@
       <c r="E2" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (MATH)</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(G.K)</t>
-        </is>
-      </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -6628,16 +6628,16 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
       <c r="M2" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -6646,14 +6646,14 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="O2" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="P2" s="7" t="inlineStr">
@@ -6671,79 +6671,79 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (ENG)</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (EVS)</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>N.NAVYA
+(ENG)</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(G.K)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>N.NAVYA
-(ENG)</t>
+          <t>K.ESWAR
+(EVS)</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
       <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="O3" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
         </is>
       </c>
       <c r="P3" s="7" t="inlineStr">
@@ -6767,7 +6767,7 @@
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -6779,55 +6779,55 @@
       <c r="F4" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(G.K)</t>
+        </is>
+      </c>
       <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
+(PHY)</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
@@ -6850,20 +6850,20 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (EVS)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(MATH)</t>
-        </is>
-      </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -6875,19 +6875,19 @@
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -6898,26 +6898,26 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
@@ -6941,73 +6941,73 @@
       <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (EVS)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
@@ -7043,7 +7043,7 @@
       <c r="E7" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -7066,22 +7066,22 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
@@ -7096,8 +7096,8 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
@@ -7121,19 +7121,19 @@
       <c r="C8" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -7145,7 +7145,7 @@
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -7156,28 +7156,28 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
@@ -7186,14 +7186,14 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>RIYA
-(HIN)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
@@ -7307,7 +7307,7 @@
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -7319,13 +7319,13 @@
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(EVS)</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -7354,16 +7354,16 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(BIO)</t>
+        </is>
+      </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -7372,20 +7372,20 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="P10" s="7" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -7409,19 +7409,19 @@
       <c r="E11" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -7438,44 +7438,44 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
 (PHY)</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -7487,25 +7487,25 @@
       <c r="C12" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (EVS)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -7516,56 +7516,56 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(PHY)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -7594,14 +7594,14 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>CHANDRAKALA
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (HIN)</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(EVS)</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -7612,38 +7612,38 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>K.ESWAR
+(PHY)</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
@@ -7654,8 +7654,8 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -7673,31 +7673,31 @@
       <c r="D14" s="7" t="inlineStr">
         <is>
           <t>BIJILI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(G.K)</t>
-        </is>
-      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>SURYA DEVI
+(ENG)</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(G.K)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -7708,44 +7708,44 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>N.NAVYA
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
+      <c r="N14" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -7763,73 +7763,73 @@
       <c r="D15" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(HIN)</t>
-        </is>
-      </c>
       <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
       <c r="P15" s="7" t="inlineStr">
@@ -7847,7 +7847,7 @@
       <c r="C16" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -7871,7 +7871,7 @@
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(G.K)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -7882,38 +7882,38 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
@@ -8004,22 +8004,22 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
           <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -8033,19 +8033,19 @@
       <c r="C18" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
 (ORAL)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -8057,7 +8057,7 @@
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
@@ -8074,8 +8074,8 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -8098,20 +8098,20 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
 (CHEM)</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -8147,61 +8147,61 @@
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
       <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>M.LALITHA
-(TEL)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
     </row>
@@ -8213,31 +8213,31 @@
       <c r="C20" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -8248,50 +8248,50 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -8309,19 +8309,19 @@
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -8338,50 +8338,50 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
         </is>
       </c>
     </row>
@@ -8393,31 +8393,31 @@
       <c r="C22" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (HIN)</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -8428,16 +8428,16 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
@@ -8452,26 +8452,26 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>D.SUMANI
-(ENG)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -8483,85 +8483,85 @@
       <c r="C23" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (MATH)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(EVS)</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -8573,19 +8573,19 @@
       <c r="C24" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -8597,7 +8597,7 @@
       <c r="G24" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -8614,8 +8614,8 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
-(SOC)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -8632,20 +8632,20 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(PHY)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
@@ -8730,22 +8730,22 @@
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -8759,13 +8759,13 @@
       <c r="C26" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -8777,7 +8777,7 @@
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -8788,28 +8788,28 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
 (EVS)</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -8825,19 +8825,19 @@
       <c r="N26" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(CHEM)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -8849,25 +8849,25 @@
       <c r="C27" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(EVS)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -8878,50 +8878,50 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="N27" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
         </is>
       </c>
       <c r="P27" s="7" t="inlineStr">
@@ -8939,37 +8939,37 @@
       <c r="C28" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (MATH)</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(ENG)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>S.GAYATHRI
+(G.K)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -8986,26 +8986,26 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
       <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (PHY)</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
@@ -9028,86 +9028,86 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(G.K)</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="N29" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="O29" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P29" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9118,26 +9118,26 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ORAL)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(EVS)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -9148,56 +9148,56 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
 (G.K)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(EVS)</t>
-        </is>
-      </c>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="M30" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
 (HIN)</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="P30" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9220,20 +9220,20 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>MAHA LAKSHMI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -9245,37 +9245,37 @@
       <c r="I31" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(G.K)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M31" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(PHY)</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
@@ -9299,7 +9299,7 @@
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -9311,7 +9311,7 @@
       <c r="E32" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -9370,8 +9370,8 @@
       </c>
       <c r="O32" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>D.GOWTHAM
+(MATH)</t>
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
@@ -9462,16 +9462,16 @@
       </c>
       <c r="O33" s="8" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
           <t>D.GOWTHAM
 (MATH)</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -9485,13 +9485,13 @@
       <c r="C34" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -9503,13 +9503,13 @@
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(MATH)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -9521,7 +9521,7 @@
       <c r="I34" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
@@ -9550,20 +9550,20 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr">
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="P34" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -9574,70 +9574,70 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>SHEKINA
+(MATH)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(TEL)</t>
+(ENG)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
+(ORAL)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(EVS)</t>
-        </is>
-      </c>
       <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I35" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
       <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="M35" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
@@ -9646,14 +9646,14 @@
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="P35" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
     </row>
@@ -9664,14 +9664,14 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(MATH)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(EVS)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -9683,67 +9683,67 @@
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>SHEKINA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
 (MATH)</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N36" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
       <c r="O36" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>CHALAPATHI
 (BIO)</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(CHEM)</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       <c r="C37" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -9773,61 +9773,61 @@
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(EVS)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(HIN)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
+          <t>VINAY
+(COMP)</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
           <t>K.ESWAR
-(G.K)</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>VINAY
-(COMP)</t>
-        </is>
-      </c>
-      <c r="N37" s="7" t="inlineStr">
+(PHY)</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O37" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
@@ -9845,13 +9845,13 @@
       <c r="C38" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ORAL)</t>
+(TEL)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -9863,13 +9863,13 @@
       <c r="F38" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
+(G.K)</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(TEL)</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -9880,34 +9880,34 @@
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L38" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="M38" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
@@ -9916,14 +9916,14 @@
       </c>
       <c r="O38" s="7" t="inlineStr">
         <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -9934,16 +9934,16 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
@@ -9953,7 +9953,7 @@
       <c r="F39" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(TEL)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -9970,44 +9970,44 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>R.KAMALA
+(SOC)</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
+          <t>P.E.T Instructor
+(P.E.T)</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
           <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
+(BIO)</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>SUNITHA
-(SOC)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>P.E.T Instructor
+(P.E.T)</t>
         </is>
       </c>
       <c r="P39" s="7" t="inlineStr">
@@ -10025,7 +10025,7 @@
       <c r="C40" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(MATH)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -10037,7 +10037,7 @@
       <c r="E40" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -10066,14 +10066,14 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
+          <t>CHANDINI
+(MATH)</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(EVS)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -10084,26 +10084,26 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>R.KAMALA
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>D.GOWTHAM
 (MATH)</t>
-        </is>
-      </c>
-      <c r="P40" s="7" t="inlineStr">
-        <is>
-          <t>RIYA
-(HIN)</t>
         </is>
       </c>
     </row>
@@ -10188,16 +10188,16 @@
       </c>
       <c r="O41" s="8" t="inlineStr">
         <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
           <t>SUNITHA
 (SOC)</t>
         </is>
       </c>
-      <c r="P41" s="8" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
@@ -10211,25 +10211,25 @@
       <c r="C42" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>CHANDRAKALA
-(ENG)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -10252,16 +10252,16 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="K42" s="7" t="inlineStr">
-        <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -10270,14 +10270,14 @@
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>CHANDINI
-(MATH)</t>
+          <t>S.GAYATHRI
+(BIO)</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
-(PHY)</t>
+(CHEM)</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
@@ -10301,25 +10301,25 @@
       <c r="C43" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
 (ENG)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ORAL)</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(MATH)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -10330,56 +10330,56 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
+          <t>S.GAYATHRI
+(EVS)</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
           <t>N.NAVYA
 (ENG)</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
       <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>VINAY
+(COMP)</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>K.ESWAR
-(CHEM)</t>
-        </is>
-      </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>VINAY
-(COMP)</t>
+          <t>SAI KEERTHI
+(HIN)</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>CHALAPATHI
+(BIO)</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>D.SUMANI
+(ENG)</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
 (TEL)</t>
-        </is>
-      </c>
-      <c r="O43" s="7" t="inlineStr">
-        <is>
-          <t>CHALAPATHI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="P43" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
         </is>
       </c>
     </row>
@@ -10390,64 +10390,64 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
+          <t>SHEKINA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(EVS)</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>S.GAYATHRI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
           <t>P.SATYAVENI
 (TEL)</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>SHEKINA
-(HIN)</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(G.K)</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="L44" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -10456,20 +10456,20 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
           <t>CHALAPATHI
 (BIO)</t>
         </is>
       </c>
-      <c r="O44" s="7" t="inlineStr">
-        <is>
-          <t>D.SUMANI
-(ENG)</t>
-        </is>
-      </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(CHEM)</t>
+          <t>SAIRAM
+(PHY)</t>
         </is>
       </c>
     </row>
@@ -10487,13 +10487,13 @@
       <c r="D45" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(ORAL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -10504,16 +10504,16 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>SURYA DEVI
-(MATH)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
           <t>VINAY
 (COMP)</t>
         </is>
       </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
@@ -10522,44 +10522,44 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>N.NAVYA
-(ENG)</t>
+          <t>S.GAYATHRI
+(EVS)</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(EVS)</t>
+          <t>P.SATYAVENI
+(TEL)</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
-      <c r="M45" s="7" t="inlineStr">
-        <is>
-          <t>SAI KEERTHI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>SAIRAM
+(PHY)</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
         <is>
           <t>D.SUMANI
 (ENG)</t>
-        </is>
-      </c>
-      <c r="O45" s="7" t="inlineStr">
-        <is>
-          <t>SAIRAM
-(PHY)</t>
-        </is>
-      </c>
-      <c r="P45" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
         </is>
       </c>
     </row>
@@ -10571,57 +10571,57 @@
       <c r="C46" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
+(MATH)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>MAHA LAKSHMI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
 (ENG)</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(EVS)</t>
-        </is>
-      </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
           <t>S.GAYATHRI
-(EVS)</t>
+(G.K)</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>P.SATYAVENI
+(TEL)</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>R.KAMALA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>SAI KEERTHI
 (HIN)</t>
         </is>
       </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>P.SATYAVENI
-(TEL)</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr">
-        <is>
-          <t>R.KAMALA
-(SOC)</t>
-        </is>
-      </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
           <t>M.LALITHA
@@ -10630,26 +10630,26 @@
       </c>
       <c r="M46" s="7" t="inlineStr">
         <is>
+          <t>K.ESWAR
+(CHEM)</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
           <t>D.SUMANI
 (ENG)</t>
         </is>
       </c>
-      <c r="N46" s="7" t="inlineStr">
-        <is>
-          <t>CHANDINI
-(MATH)</t>
-        </is>
-      </c>
       <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>SUNITHA
+(SOC)</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>RIYA
 (HIN)</t>
-        </is>
-      </c>
-      <c r="P46" s="7" t="inlineStr">
-        <is>
-          <t>SUNITHA
-(SOC)</t>
         </is>
       </c>
     </row>
@@ -10660,58 +10660,58 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>SHEKINA
-(ENG)</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>BIJILI
-(HIN)</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>MAHA LAKSHMI
-(ENG)</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>CHANDRAKALA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>BIJILI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(EVS)</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>CHANDRAKALA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>SURYA DEVI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>P.E.T Instructor
 (P.E.T)</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>SAI KEERTHI
+(HIN)</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>CHANDINI
 (MATH)</t>
         </is>
       </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>K.ESWAR
+(EVS)</t>
+        </is>
+      </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
           <t>N.NAVYA
@@ -10720,26 +10720,26 @@
       </c>
       <c r="M47" s="7" t="inlineStr">
         <is>
-          <t>K.ESWAR
-(G.K)</t>
+          <t>D.SUMANI
+(ENG)</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>M.LALITHA
+(TEL)</t>
+        </is>
+      </c>
+      <c r="O47" s="7" t="inlineStr">
+        <is>
+          <t>D.GOWTHAM
+(MATH)</t>
+        </is>
+      </c>
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
-        </is>
-      </c>
-      <c r="O47" s="7" t="inlineStr">
-        <is>
-          <t>D.GOWTHAM
-(MATH)</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>P.E.T Instructor
-(P.E.T)</t>
         </is>
       </c>
     </row>
@@ -10751,19 +10751,19 @@
       <c r="C48" s="7" t="inlineStr">
         <is>
           <t>SHEKINA
-(EVS)</t>
+(MATH)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
           <t>BIJILI
-(ENG)</t>
+(HIN)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
           <t>MAHA LAKSHMI
-(MATH)</t>
+(ORAL)</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -10775,7 +10775,7 @@
       <c r="G48" s="7" t="inlineStr">
         <is>
           <t>SURYA DEVI
-(TEL)</t>
+(EVS)</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -10786,44 +10786,44 @@
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>P.SATYAVENI
-(TEL)</t>
+          <t>S.GAYATHRI
+(EVS)</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>N.NAVYA
+(ENG)</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>R.KAMALA
 (SOC)</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>N.NAVYA
-(ENG)</t>
-        </is>
-      </c>
       <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>S.GAYATHRI
-(BIO)</t>
-        </is>
-      </c>
-      <c r="M48" s="7" t="inlineStr">
-        <is>
-          <t>M.LALITHA
-(TEL)</t>
-        </is>
-      </c>
-      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>K.ESWAR
 (CHEM)</t>
         </is>
       </c>
-      <c r="O48" s="7" t="inlineStr">
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>CHANDINI
+(MATH)</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
         <is>
           <t>SUNITHA
 (SOC)</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>RIYA
+(HIN)</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">

--- a/NRHS/Output/NRHS_Timetable_Final.xlsx
+++ b/NRHS/Output/NRHS_Timetable_Final.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -148,11 +148,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -184,6 +217,8 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6331,7 +6366,15 @@
       <c r="F196" s="7" t="inlineStr"/>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>Class 8 (KAR)</t>
+          <t>Class 1(A) (KAR)
+Class 1(B) (KAR)
+Class 2 (KAR)
+Class 3 (KAR)
+Class 4 (KAR)
+Class 5 (KAR)
+Class 6 (KAR)
+Class 7 (KAR)
+Class 8 (KAR)</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr"/>
@@ -6457,12 +6500,22 @@
       <c r="F203" s="7" t="inlineStr"/>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>LKG (P.E.T)
+UKG(A) (P.E.T)
+UKG(B) (P.E.T)
+Class 1(A) (P.E.T)
+Class 1(B) (P.E.T)
+Class 2 (P.E.T)
+Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>Class 6 (P.E.T)
+Class 7 (P.E.T)
+Class 8 (P.E.T)
+Class 9 (P.E.T)
+Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="I203" s="7" t="inlineStr"/>
@@ -6480,12 +6533,20 @@
       <c r="F204" s="7" t="inlineStr"/>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
+          <t>UKG(A) (P.E.T)
+Class 1(A) (P.E.T)
+Class 1(B) (P.E.T)
+Class 2 (P.E.T)
+Class 3 (P.E.T)
+Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>Class 10 (P.E.T)</t>
+          <t>Class 6 (P.E.T)
+Class 7 (P.E.T)
+Class 8 (P.E.T)
+Class 10 (P.E.T)</t>
         </is>
       </c>
       <c r="I204" s="7" t="inlineStr"/>
@@ -6522,7 +6583,11 @@
       <c r="F206" s="7" t="inlineStr"/>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>Class 5 (P.E.T)</t>
+          <t>LKG (P.E.T)
+UKG(A) (P.E.T)
+UKG(B) (P.E.T)
+Class 2 (P.E.T)
+Class 5 (P.E.T)</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr"/>
@@ -6541,7 +6606,13 @@
       <c r="F207" s="7" t="inlineStr"/>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>Class 4 (P.E.T)</t>
+          <t>LKG (P.E.T)
+UKG(B) (P.E.T)
+Class 1(A) (P.E.T)
+Class 1(B) (P.E.T)
+Class 2 (P.E.T)
+Class 3 (P.E.T)
+Class 4 (P.E.T)</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr"/>
@@ -6797,7 +6868,7 @@
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="11" t="n"/>
+      <c r="A3" s="13" t="n"/>
       <c r="B3" s="6" t="n">
         <v>2</v>
       </c>
@@ -6887,7 +6958,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="11" t="n"/>
+      <c r="A4" s="13" t="n"/>
       <c r="B4" s="6" t="n">
         <v>3</v>
       </c>
@@ -6977,7 +7048,7 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="11" t="n"/>
+      <c r="A5" s="13" t="n"/>
       <c r="B5" s="6" t="n">
         <v>4</v>
       </c>
@@ -7067,7 +7138,7 @@
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="13" t="n"/>
       <c r="B6" s="6" t="n">
         <v>5</v>
       </c>
@@ -7157,7 +7228,7 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="13" t="n"/>
       <c r="B7" s="6" t="n">
         <v>6</v>
       </c>
@@ -7247,7 +7318,7 @@
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="13" t="n"/>
       <c r="B8" s="6" t="n">
         <v>7</v>
       </c>
@@ -7337,7 +7408,7 @@
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="11" t="n"/>
+      <c r="A9" s="14" t="n"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Study Hour</t>
@@ -7523,7 +7594,7 @@
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="11" t="n"/>
+      <c r="A11" s="13" t="n"/>
       <c r="B11" s="6" t="n">
         <v>2</v>
       </c>
@@ -7613,7 +7684,7 @@
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="11" t="n"/>
+      <c r="A12" s="13" t="n"/>
       <c r="B12" s="6" t="n">
         <v>3</v>
       </c>
@@ -7703,7 +7774,7 @@
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="13" t="n"/>
       <c r="B13" s="6" t="n">
         <v>4</v>
       </c>
@@ -7793,7 +7864,7 @@
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="13" t="n"/>
       <c r="B14" s="6" t="n">
         <v>5</v>
       </c>
@@ -7883,7 +7954,7 @@
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="13" t="n"/>
       <c r="B15" s="6" t="n">
         <v>6</v>
       </c>
@@ -7973,7 +8044,7 @@
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="n"/>
+      <c r="A16" s="13" t="n"/>
       <c r="B16" s="6" t="n">
         <v>7</v>
       </c>
@@ -8063,7 +8134,7 @@
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="11" t="n"/>
+      <c r="A17" s="14" t="n"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Study Hour</t>
@@ -8249,7 +8320,7 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="13" t="n"/>
       <c r="B19" s="6" t="n">
         <v>2</v>
       </c>
@@ -8339,7 +8410,7 @@
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="13" t="n"/>
       <c r="B20" s="6" t="n">
         <v>3</v>
       </c>
@@ -8429,7 +8500,7 @@
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="13" t="n"/>
       <c r="B21" s="6" t="n">
         <v>4</v>
       </c>
@@ -8519,7 +8590,7 @@
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="13" t="n"/>
       <c r="B22" s="6" t="n">
         <v>5</v>
       </c>
@@ -8609,7 +8680,7 @@
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="11" t="n"/>
+      <c r="A23" s="13" t="n"/>
       <c r="B23" s="6" t="n">
         <v>6</v>
       </c>
@@ -8699,7 +8770,7 @@
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="11" t="n"/>
+      <c r="A24" s="13" t="n"/>
       <c r="B24" s="6" t="n">
         <v>7</v>
       </c>
@@ -8789,7 +8860,7 @@
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="11" t="n"/>
+      <c r="A25" s="14" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Study Hour</t>
@@ -8975,7 +9046,7 @@
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="11" t="n"/>
+      <c r="A27" s="13" t="n"/>
       <c r="B27" s="6" t="n">
         <v>2</v>
       </c>
@@ -9065,7 +9136,7 @@
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="11" t="n"/>
+      <c r="A28" s="13" t="n"/>
       <c r="B28" s="6" t="n">
         <v>3</v>
       </c>
@@ -9155,7 +9226,7 @@
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="11" t="n"/>
+      <c r="A29" s="13" t="n"/>
       <c r="B29" s="6" t="n">
         <v>4</v>
       </c>
@@ -9245,7 +9316,7 @@
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="11" t="n"/>
+      <c r="A30" s="13" t="n"/>
       <c r="B30" s="6" t="n">
         <v>5</v>
       </c>
@@ -9335,7 +9406,7 @@
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="11" t="n"/>
+      <c r="A31" s="13" t="n"/>
       <c r="B31" s="6" t="n">
         <v>6</v>
       </c>
@@ -9425,7 +9496,7 @@
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="11" t="n"/>
+      <c r="A32" s="13" t="n"/>
       <c r="B32" s="6" t="n">
         <v>7</v>
       </c>
@@ -9515,7 +9586,7 @@
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="11" t="n"/>
+      <c r="A33" s="14" t="n"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Study Hour</t>
@@ -9701,7 +9772,7 @@
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="11" t="n"/>
+      <c r="A35" s="13" t="n"/>
       <c r="B35" s="6" t="n">
         <v>2</v>
       </c>
@@ -9791,7 +9862,7 @@
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="11" t="n"/>
+      <c r="A36" s="13" t="n"/>
       <c r="B36" s="6" t="n">
         <v>3</v>
       </c>
@@ -9881,7 +9952,7 @@
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="11" t="n"/>
+      <c r="A37" s="13" t="n"/>
       <c r="B37" s="6" t="n">
         <v>4</v>
       </c>
@@ -9971,7 +10042,7 @@
       </c>
     </row>
     <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="11" t="n"/>
+      <c r="A38" s="13" t="n"/>
       <c r="B38" s="6" t="n">
         <v>5</v>
       </c>
@@ -10061,7 +10132,7 @@
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="11" t="n"/>
+      <c r="A39" s="13" t="n"/>
       <c r="B39" s="6" t="n">
         <v>6</v>
       </c>
@@ -10151,7 +10222,7 @@
       </c>
     </row>
     <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="11" t="n"/>
+      <c r="A40" s="13" t="n"/>
       <c r="B40" s="6" t="n">
         <v>7</v>
       </c>
@@ -10241,7 +10312,7 @@
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="11" t="n"/>
+      <c r="A41" s="14" t="n"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Study Hour</t>
@@ -10427,7 +10498,7 @@
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="11" t="n"/>
+      <c r="A43" s="13" t="n"/>
       <c r="B43" s="6" t="n">
         <v>2</v>
       </c>
@@ -10517,7 +10588,7 @@
       </c>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="11" t="n"/>
+      <c r="A44" s="13" t="n"/>
       <c r="B44" s="6" t="n">
         <v>3</v>
       </c>
@@ -10607,7 +10678,7 @@
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="11" t="n"/>
+      <c r="A45" s="13" t="n"/>
       <c r="B45" s="6" t="n">
         <v>4</v>
       </c>
@@ -10697,7 +10768,7 @@
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="11" t="n"/>
+      <c r="A46" s="13" t="n"/>
       <c r="B46" s="6" t="n">
         <v>5</v>
       </c>
@@ -10787,7 +10858,7 @@
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="11" t="n"/>
+      <c r="A47" s="13" t="n"/>
       <c r="B47" s="6" t="n">
         <v>6</v>
       </c>
@@ -10877,7 +10948,7 @@
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="11" t="n"/>
+      <c r="A48" s="13" t="n"/>
       <c r="B48" s="6" t="n">
         <v>7</v>
       </c>
@@ -10967,7 +11038,7 @@
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="11" t="n"/>
+      <c r="A49" s="14" t="n"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Study Hour</t>
